--- a/data/a_01_mortality_data_processed/cod_algorithm/final_kw_v1.xlsx
+++ b/data/a_01_mortality_data_processed/cod_algorithm/final_kw_v1.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/gabrieladaza/Documents/GitHub/harmonized_carceral_mortality_data/data/a_01_mortality_data_processed/fitting_mci_doc_cod/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/gabrieladaza/Documents/GitHub/harmonized_carceral_mortality_data/data/a_01_mortality_data_processed/cod_algorithm/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{85D079B0-C23E-874B-9DD4-31510045D17B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EAF8AB39-60E8-2D44-9C76-4FD72F38C685}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="760" windowWidth="30240" windowHeight="17540" firstSheet="1" activeTab="5" xr2:uid="{A6ED5751-AE0F-B045-AA43-8F95CA62E1A7}"/>
+    <workbookView xWindow="0" yWindow="760" windowWidth="30240" windowHeight="17540" firstSheet="1" activeTab="2" xr2:uid="{A6ED5751-AE0F-B045-AA43-8F95CA62E1A7}"/>
   </bookViews>
   <sheets>
     <sheet name="sheet_names" sheetId="6" r:id="rId1"/>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1443" uniqueCount="360">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1438" uniqueCount="356">
   <si>
     <t>DIABETES</t>
   </si>
@@ -868,9 +868,6 @@
     <t>GASTROINTESTINAL HEMORRHAGE</t>
   </si>
   <si>
-    <t xml:space="preserve">**natural causes? </t>
-  </si>
-  <si>
     <t xml:space="preserve">ACUTE MYELOID LEUKEMIA </t>
   </si>
   <si>
@@ -934,9 +931,6 @@
     <t>ASCVD</t>
   </si>
   <si>
-    <t>ASPHXIA</t>
-  </si>
-  <si>
     <t>CA OF RECTUM</t>
   </si>
   <si>
@@ -946,9 +940,6 @@
     <t>ESLD</t>
   </si>
   <si>
-    <t>EXSANGUINATION</t>
-  </si>
-  <si>
     <t>HEPATORENAL SYNDROME</t>
   </si>
   <si>
@@ -959,9 +950,6 @@
   </si>
   <si>
     <t>SUICIDE</t>
-  </si>
-  <si>
-    <t xml:space="preserve">*currently stopped at line 69 (5 n or more) </t>
   </si>
   <si>
     <t>k</t>
@@ -1522,42 +1510,42 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
-        <v>313</v>
+        <v>309</v>
       </c>
       <c r="B1" t="s">
-        <v>314</v>
+        <v>310</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
+        <v>311</v>
+      </c>
+      <c r="B2" t="s">
         <v>315</v>
-      </c>
-      <c r="B2" t="s">
-        <v>319</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
+        <v>312</v>
+      </c>
+      <c r="B3" t="s">
         <v>316</v>
-      </c>
-      <c r="B3" t="s">
-        <v>320</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
+        <v>313</v>
+      </c>
+      <c r="B4" t="s">
         <v>317</v>
-      </c>
-      <c r="B4" t="s">
-        <v>321</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
+        <v>314</v>
+      </c>
+      <c r="B5" t="s">
         <v>318</v>
-      </c>
-      <c r="B5" t="s">
-        <v>322</v>
       </c>
     </row>
   </sheetData>
@@ -1968,7 +1956,7 @@
         <v>27</v>
       </c>
       <c r="G14" s="1" t="s">
-        <v>307</v>
+        <v>303</v>
       </c>
       <c r="H14" s="1"/>
       <c r="I14" s="1"/>
@@ -6163,22 +6151,17 @@
       <c r="K1" s="4" t="s">
         <v>233</v>
       </c>
-      <c r="M1" s="4" t="s">
-        <v>275</v>
-      </c>
+      <c r="M1" s="4"/>
     </row>
     <row r="2" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
-        <v>308</v>
+        <v>304</v>
       </c>
       <c r="B2" t="s">
         <v>246</v>
       </c>
       <c r="F2" s="1" t="s">
         <v>237</v>
-      </c>
-      <c r="M2" t="s">
-        <v>297</v>
       </c>
     </row>
     <row r="3" spans="1:13" x14ac:dyDescent="0.2">
@@ -6191,9 +6174,6 @@
       <c r="F3" s="1" t="s">
         <v>238</v>
       </c>
-      <c r="M3" t="s">
-        <v>301</v>
-      </c>
     </row>
     <row r="4" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
@@ -6205,9 +6185,6 @@
       <c r="F4" s="1" t="s">
         <v>239</v>
       </c>
-      <c r="M4" t="s">
-        <v>305</v>
-      </c>
     </row>
     <row r="5" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
@@ -6219,9 +6196,6 @@
       <c r="F5" s="1" t="s">
         <v>240</v>
       </c>
-      <c r="M5" t="s">
-        <v>306</v>
-      </c>
     </row>
     <row r="6" spans="1:13" x14ac:dyDescent="0.2">
       <c r="B6" t="s">
@@ -6233,7 +6207,7 @@
     </row>
     <row r="7" spans="1:13" x14ac:dyDescent="0.2">
       <c r="B7" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="F7" s="1" t="s">
         <v>243</v>
@@ -6371,132 +6345,132 @@
     </row>
     <row r="34" spans="6:6" x14ac:dyDescent="0.2">
       <c r="F34" s="1" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
     </row>
     <row r="35" spans="6:6" x14ac:dyDescent="0.2">
       <c r="F35" s="1" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
     </row>
     <row r="36" spans="6:6" x14ac:dyDescent="0.2">
       <c r="F36" s="1" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
     </row>
     <row r="37" spans="6:6" x14ac:dyDescent="0.2">
       <c r="F37" s="1" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
     </row>
     <row r="38" spans="6:6" x14ac:dyDescent="0.2">
       <c r="F38" s="1" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
     </row>
     <row r="39" spans="6:6" x14ac:dyDescent="0.2">
       <c r="F39" s="1" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
     </row>
     <row r="40" spans="6:6" x14ac:dyDescent="0.2">
       <c r="F40" s="1" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
     </row>
     <row r="41" spans="6:6" x14ac:dyDescent="0.2">
       <c r="F41" s="1" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
     </row>
     <row r="42" spans="6:6" x14ac:dyDescent="0.2">
       <c r="F42" s="1" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
     </row>
     <row r="43" spans="6:6" x14ac:dyDescent="0.2">
       <c r="F43" s="1" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
     </row>
     <row r="44" spans="6:6" x14ac:dyDescent="0.2">
       <c r="F44" s="1" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
     </row>
     <row r="45" spans="6:6" x14ac:dyDescent="0.2">
       <c r="F45" s="1" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
     </row>
     <row r="46" spans="6:6" x14ac:dyDescent="0.2">
       <c r="F46" s="1" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
     </row>
     <row r="47" spans="6:6" x14ac:dyDescent="0.2">
       <c r="F47" s="1" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
     </row>
     <row r="48" spans="6:6" x14ac:dyDescent="0.2">
       <c r="F48" s="1" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
     </row>
     <row r="49" spans="6:6" x14ac:dyDescent="0.2">
       <c r="F49" s="1" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
     </row>
     <row r="50" spans="6:6" x14ac:dyDescent="0.2">
       <c r="F50" s="1" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
     </row>
     <row r="51" spans="6:6" x14ac:dyDescent="0.2">
       <c r="F51" s="1" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
     </row>
     <row r="52" spans="6:6" x14ac:dyDescent="0.2">
       <c r="F52" s="1" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
     </row>
     <row r="53" spans="6:6" x14ac:dyDescent="0.2">
       <c r="F53" s="1" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
     </row>
     <row r="54" spans="6:6" x14ac:dyDescent="0.2">
       <c r="F54" s="1" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
     </row>
     <row r="55" spans="6:6" x14ac:dyDescent="0.2">
       <c r="F55" s="1" t="s">
-        <v>299</v>
+        <v>297</v>
       </c>
     </row>
     <row r="56" spans="6:6" x14ac:dyDescent="0.2">
       <c r="F56" s="1" t="s">
-        <v>300</v>
+        <v>298</v>
       </c>
     </row>
     <row r="57" spans="6:6" x14ac:dyDescent="0.2">
       <c r="F57" s="1" t="s">
-        <v>302</v>
+        <v>299</v>
       </c>
     </row>
     <row r="58" spans="6:6" x14ac:dyDescent="0.2">
       <c r="F58" s="1" t="s">
-        <v>303</v>
+        <v>300</v>
       </c>
     </row>
     <row r="59" spans="6:6" x14ac:dyDescent="0.2">
       <c r="F59" s="1" t="s">
-        <v>304</v>
+        <v>301</v>
       </c>
     </row>
   </sheetData>
@@ -7318,7 +7292,7 @@
         <v>114</v>
       </c>
       <c r="B33" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="C33" s="1"/>
       <c r="D33" s="1"/>
@@ -8546,7 +8520,7 @@
       <c r="D121" s="1"/>
       <c r="E121" s="1"/>
       <c r="F121" s="1" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="G121" s="1"/>
       <c r="H121" s="1"/>
@@ -8559,7 +8533,7 @@
       <c r="D122" s="1"/>
       <c r="E122" s="1"/>
       <c r="F122" s="1" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="G122" s="1"/>
       <c r="H122" s="1"/>
@@ -8572,7 +8546,7 @@
       <c r="D123" s="1"/>
       <c r="E123" s="1"/>
       <c r="F123" s="1" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="G123" s="1"/>
       <c r="H123" s="1"/>
@@ -8585,7 +8559,7 @@
       <c r="D124" s="1"/>
       <c r="E124" s="1"/>
       <c r="F124" s="1" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="G124" s="1"/>
       <c r="H124" s="1"/>
@@ -8598,7 +8572,7 @@
       <c r="D125" s="1"/>
       <c r="E125" s="1"/>
       <c r="F125" s="1" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="G125" s="1"/>
       <c r="H125" s="1"/>
@@ -8611,7 +8585,7 @@
       <c r="D126" s="1"/>
       <c r="E126" s="1"/>
       <c r="F126" s="1" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="G126" s="1"/>
       <c r="H126" s="1"/>
@@ -8624,7 +8598,7 @@
       <c r="D127" s="1"/>
       <c r="E127" s="1"/>
       <c r="F127" s="1" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="G127" s="1"/>
       <c r="H127" s="1"/>
@@ -8637,7 +8611,7 @@
       <c r="D128" s="1"/>
       <c r="E128" s="1"/>
       <c r="F128" s="1" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="G128" s="1"/>
       <c r="H128" s="1"/>
@@ -8650,7 +8624,7 @@
       <c r="D129" s="1"/>
       <c r="E129" s="1"/>
       <c r="F129" s="1" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="G129" s="1"/>
       <c r="H129" s="1"/>
@@ -8663,7 +8637,7 @@
       <c r="D130" s="1"/>
       <c r="E130" s="1"/>
       <c r="F130" s="1" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="G130" s="1"/>
       <c r="H130" s="1"/>
@@ -8676,7 +8650,7 @@
       <c r="D131" s="1"/>
       <c r="E131" s="1"/>
       <c r="F131" s="1" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="G131" s="1"/>
       <c r="H131" s="1"/>
@@ -8689,7 +8663,7 @@
       <c r="D132" s="1"/>
       <c r="E132" s="1"/>
       <c r="F132" s="1" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="G132" s="1"/>
       <c r="H132" s="1"/>
@@ -8702,7 +8676,7 @@
       <c r="D133" s="1"/>
       <c r="E133" s="1"/>
       <c r="F133" s="1" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="G133" s="1"/>
       <c r="H133" s="1"/>
@@ -8715,7 +8689,7 @@
       <c r="D134" s="1"/>
       <c r="E134" s="1"/>
       <c r="F134" s="1" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="G134" s="1"/>
       <c r="H134" s="1"/>
@@ -8728,7 +8702,7 @@
       <c r="D135" s="1"/>
       <c r="E135" s="1"/>
       <c r="F135" s="1" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="G135" s="1"/>
       <c r="H135" s="1"/>
@@ -8741,7 +8715,7 @@
       <c r="D136" s="1"/>
       <c r="E136" s="1"/>
       <c r="F136" s="1" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="G136" s="1"/>
       <c r="H136" s="1"/>
@@ -8754,7 +8728,7 @@
       <c r="D137" s="1"/>
       <c r="E137" s="1"/>
       <c r="F137" s="1" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="G137" s="1"/>
       <c r="H137" s="1"/>
@@ -8767,7 +8741,7 @@
       <c r="D138" s="1"/>
       <c r="E138" s="1"/>
       <c r="F138" s="1" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="G138" s="1"/>
       <c r="H138" s="1"/>
@@ -8780,7 +8754,7 @@
       <c r="D139" s="1"/>
       <c r="E139" s="1"/>
       <c r="F139" s="1" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="G139" s="1"/>
       <c r="H139" s="1"/>
@@ -8793,7 +8767,7 @@
       <c r="D140" s="1"/>
       <c r="E140" s="1"/>
       <c r="F140" s="1" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="G140" s="1"/>
       <c r="H140" s="1"/>
@@ -8806,7 +8780,7 @@
       <c r="D141" s="1"/>
       <c r="E141" s="1"/>
       <c r="F141" s="1" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="G141" s="1"/>
       <c r="H141" s="1"/>
@@ -8819,7 +8793,7 @@
       <c r="D142" s="1"/>
       <c r="E142" s="1"/>
       <c r="F142" s="1" t="s">
-        <v>299</v>
+        <v>297</v>
       </c>
       <c r="G142" s="1"/>
       <c r="H142" s="1"/>
@@ -8832,7 +8806,7 @@
       <c r="D143" s="1"/>
       <c r="E143" s="1"/>
       <c r="F143" s="1" t="s">
-        <v>300</v>
+        <v>298</v>
       </c>
       <c r="G143" s="1"/>
       <c r="H143" s="1"/>
@@ -8845,7 +8819,7 @@
       <c r="D144" s="1"/>
       <c r="E144" s="1"/>
       <c r="F144" s="1" t="s">
-        <v>302</v>
+        <v>299</v>
       </c>
       <c r="G144" s="1"/>
       <c r="H144" s="1"/>
@@ -8858,7 +8832,7 @@
       <c r="D145" s="1"/>
       <c r="E145" s="1"/>
       <c r="F145" s="1" t="s">
-        <v>303</v>
+        <v>300</v>
       </c>
       <c r="G145" s="1"/>
       <c r="H145" s="1"/>
@@ -8871,7 +8845,7 @@
       <c r="D146" s="1"/>
       <c r="E146" s="1"/>
       <c r="F146" s="1" t="s">
-        <v>304</v>
+        <v>301</v>
       </c>
       <c r="G146" s="1"/>
       <c r="H146" s="1"/>
@@ -11208,10 +11182,10 @@
         <v>222</v>
       </c>
       <c r="D1" s="3" t="s">
-        <v>309</v>
+        <v>305</v>
       </c>
       <c r="E1" s="3" t="s">
-        <v>310</v>
+        <v>306</v>
       </c>
       <c r="F1" s="3" t="s">
         <v>221</v>
@@ -11220,10 +11194,10 @@
         <v>224</v>
       </c>
       <c r="H1" s="4" t="s">
-        <v>311</v>
+        <v>307</v>
       </c>
       <c r="I1" s="3" t="s">
-        <v>312</v>
+        <v>308</v>
       </c>
       <c r="J1" s="3" t="s">
         <v>18</v>
@@ -11316,7 +11290,7 @@
         <v>50</v>
       </c>
       <c r="D4" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="E4" s="1" t="s">
         <v>175</v>
@@ -11542,7 +11516,7 @@
         <v>170</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>305</v>
+        <v>302</v>
       </c>
       <c r="E12" s="1" t="s">
         <v>133</v>
@@ -11569,7 +11543,7 @@
         <v>166</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>323</v>
+        <v>319</v>
       </c>
       <c r="E13" s="1" t="s">
         <v>131</v>
@@ -11622,7 +11596,7 @@
       </c>
       <c r="D15" s="1"/>
       <c r="E15" s="1" t="s">
-        <v>324</v>
+        <v>320</v>
       </c>
       <c r="F15" s="1" t="s">
         <v>2</v>
@@ -11647,7 +11621,7 @@
       </c>
       <c r="D16" s="1"/>
       <c r="E16" s="1" t="s">
-        <v>325</v>
+        <v>321</v>
       </c>
       <c r="F16" s="1" t="s">
         <v>137</v>
@@ -13287,7 +13261,7 @@
       <c r="G117" s="1"/>
       <c r="H117" s="1"/>
       <c r="I117" s="1" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="J117" s="1"/>
     </row>
@@ -13301,7 +13275,7 @@
       <c r="G118" s="1"/>
       <c r="H118" s="1"/>
       <c r="I118" s="1" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="J118" s="1"/>
     </row>
@@ -13315,7 +13289,7 @@
       <c r="G119" s="1"/>
       <c r="H119" s="1"/>
       <c r="I119" s="1" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="J119" s="1"/>
     </row>
@@ -13329,7 +13303,7 @@
       <c r="G120" s="1"/>
       <c r="H120" s="1"/>
       <c r="I120" s="1" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="J120" s="1"/>
     </row>
@@ -13343,7 +13317,7 @@
       <c r="G121" s="1"/>
       <c r="H121" s="1"/>
       <c r="I121" s="1" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="J121" s="1"/>
     </row>
@@ -13357,7 +13331,7 @@
       <c r="G122" s="1"/>
       <c r="H122" s="1"/>
       <c r="I122" s="1" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="J122" s="1"/>
     </row>
@@ -13371,7 +13345,7 @@
       <c r="G123" s="1"/>
       <c r="H123" s="1"/>
       <c r="I123" s="1" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="J123" s="1"/>
     </row>
@@ -13385,7 +13359,7 @@
       <c r="G124" s="1"/>
       <c r="H124" s="1"/>
       <c r="I124" s="1" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="J124" s="1"/>
     </row>
@@ -13399,7 +13373,7 @@
       <c r="G125" s="1"/>
       <c r="H125" s="1"/>
       <c r="I125" s="1" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="J125" s="1"/>
     </row>
@@ -13413,7 +13387,7 @@
       <c r="G126" s="1"/>
       <c r="H126" s="1"/>
       <c r="I126" s="1" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="J126" s="1"/>
     </row>
@@ -13427,7 +13401,7 @@
       <c r="G127" s="1"/>
       <c r="H127" s="1"/>
       <c r="I127" s="1" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="J127" s="1"/>
     </row>
@@ -13441,7 +13415,7 @@
       <c r="G128" s="1"/>
       <c r="H128" s="1"/>
       <c r="I128" s="1" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="J128" s="1"/>
     </row>
@@ -13455,7 +13429,7 @@
       <c r="G129" s="1"/>
       <c r="H129" s="1"/>
       <c r="I129" s="1" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="J129" s="1"/>
     </row>
@@ -13469,7 +13443,7 @@
       <c r="G130" s="1"/>
       <c r="H130" s="1"/>
       <c r="I130" s="1" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="J130" s="1"/>
     </row>
@@ -13483,7 +13457,7 @@
       <c r="G131" s="1"/>
       <c r="H131" s="1"/>
       <c r="I131" s="1" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="J131" s="1"/>
     </row>
@@ -13497,7 +13471,7 @@
       <c r="G132" s="1"/>
       <c r="H132" s="1"/>
       <c r="I132" s="1" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="J132" s="1"/>
     </row>
@@ -13511,7 +13485,7 @@
       <c r="G133" s="1"/>
       <c r="H133" s="1"/>
       <c r="I133" s="1" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="J133" s="1"/>
     </row>
@@ -13525,7 +13499,7 @@
       <c r="G134" s="1"/>
       <c r="H134" s="1"/>
       <c r="I134" s="1" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="J134" s="1"/>
     </row>
@@ -13539,7 +13513,7 @@
       <c r="G135" s="1"/>
       <c r="H135" s="1"/>
       <c r="I135" s="1" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="J135" s="1"/>
     </row>
@@ -13553,7 +13527,7 @@
       <c r="G136" s="1"/>
       <c r="H136" s="1"/>
       <c r="I136" s="1" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="J136" s="1"/>
     </row>
@@ -13567,7 +13541,7 @@
       <c r="G137" s="1"/>
       <c r="H137" s="1"/>
       <c r="I137" s="1" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="J137" s="1"/>
     </row>
@@ -13581,7 +13555,7 @@
       <c r="G138" s="1"/>
       <c r="H138" s="1"/>
       <c r="I138" s="1" t="s">
-        <v>299</v>
+        <v>297</v>
       </c>
       <c r="J138" s="1"/>
     </row>
@@ -13595,7 +13569,7 @@
       <c r="G139" s="1"/>
       <c r="H139" s="1"/>
       <c r="I139" s="1" t="s">
-        <v>300</v>
+        <v>298</v>
       </c>
       <c r="J139" s="1"/>
     </row>
@@ -13609,7 +13583,7 @@
       <c r="G140" s="1"/>
       <c r="H140" s="1"/>
       <c r="I140" s="1" t="s">
-        <v>302</v>
+        <v>299</v>
       </c>
       <c r="J140" s="1"/>
     </row>
@@ -13623,7 +13597,7 @@
       <c r="G141" s="1"/>
       <c r="H141" s="1"/>
       <c r="I141" s="1" t="s">
-        <v>303</v>
+        <v>300</v>
       </c>
       <c r="J141" s="1"/>
     </row>
@@ -13637,7 +13611,7 @@
       <c r="G142" s="1"/>
       <c r="H142" s="1"/>
       <c r="I142" s="1" t="s">
-        <v>304</v>
+        <v>301</v>
       </c>
       <c r="J142" s="1"/>
     </row>
@@ -16222,31 +16196,31 @@
         <v>222</v>
       </c>
       <c r="D1" s="3" t="s">
-        <v>309</v>
+        <v>305</v>
       </c>
       <c r="E1" s="3" t="s">
-        <v>310</v>
+        <v>306</v>
       </c>
       <c r="F1" s="4" t="s">
-        <v>326</v>
+        <v>322</v>
       </c>
       <c r="G1" s="4" t="s">
+        <v>344</v>
+      </c>
+      <c r="H1" s="4" t="s">
+        <v>324</v>
+      </c>
+      <c r="I1" s="4" t="s">
+        <v>323</v>
+      </c>
+      <c r="J1" s="4" t="s">
+        <v>307</v>
+      </c>
+      <c r="K1" s="6" t="s">
+        <v>341</v>
+      </c>
+      <c r="L1" s="6" t="s">
         <v>348</v>
-      </c>
-      <c r="H1" s="4" t="s">
-        <v>328</v>
-      </c>
-      <c r="I1" s="4" t="s">
-        <v>327</v>
-      </c>
-      <c r="J1" s="4" t="s">
-        <v>311</v>
-      </c>
-      <c r="K1" s="6" t="s">
-        <v>345</v>
-      </c>
-      <c r="L1" s="6" t="s">
-        <v>352</v>
       </c>
       <c r="M1" s="3" t="s">
         <v>18</v>
@@ -16255,7 +16229,7 @@
         <v>221</v>
       </c>
       <c r="O1" t="s">
-        <v>349</v>
+        <v>345</v>
       </c>
     </row>
     <row r="2" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -16281,7 +16255,7 @@
         <v>270</v>
       </c>
       <c r="H2" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="I2" t="s">
         <v>242</v>
@@ -16293,7 +16267,7 @@
         <v>216</v>
       </c>
       <c r="L2" s="7" t="s">
-        <v>353</v>
+        <v>349</v>
       </c>
       <c r="M2" s="1" t="s">
         <v>18</v>
@@ -16302,7 +16276,7 @@
         <v>4</v>
       </c>
       <c r="O2" t="s">
-        <v>350</v>
+        <v>346</v>
       </c>
     </row>
     <row r="3" spans="1:15" ht="16" x14ac:dyDescent="0.2">
@@ -16325,10 +16299,10 @@
         <v>210</v>
       </c>
       <c r="G3" t="s">
-        <v>335</v>
+        <v>331</v>
       </c>
       <c r="H3" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="I3" t="s">
         <v>244</v>
@@ -16340,7 +16314,7 @@
         <v>198</v>
       </c>
       <c r="L3" s="7" t="s">
-        <v>354</v>
+        <v>350</v>
       </c>
       <c r="M3" s="1" t="s">
         <v>1</v>
@@ -16349,7 +16323,7 @@
         <v>42</v>
       </c>
       <c r="O3" t="s">
-        <v>351</v>
+        <v>347</v>
       </c>
     </row>
     <row r="4" spans="1:15" x14ac:dyDescent="0.2">
@@ -16363,7 +16337,7 @@
         <v>50</v>
       </c>
       <c r="D4" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="E4" s="1" t="s">
         <v>51</v>
@@ -16372,13 +16346,13 @@
         <v>61</v>
       </c>
       <c r="G4" t="s">
-        <v>336</v>
+        <v>332</v>
       </c>
       <c r="H4" t="s">
         <v>272</v>
       </c>
       <c r="I4" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="J4" s="1" t="s">
         <v>85</v>
@@ -16387,7 +16361,7 @@
         <v>15</v>
       </c>
       <c r="L4" s="7" t="s">
-        <v>355</v>
+        <v>351</v>
       </c>
       <c r="M4" s="1" t="s">
         <v>56</v>
@@ -16410,7 +16384,7 @@
         <v>246</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>324</v>
+        <v>320</v>
       </c>
       <c r="F5" s="1" t="s">
         <v>199</v>
@@ -16419,7 +16393,7 @@
         <v>204</v>
       </c>
       <c r="H5" t="s">
-        <v>330</v>
+        <v>326</v>
       </c>
       <c r="I5" t="s">
         <v>187</v>
@@ -16431,7 +16405,7 @@
         <v>245</v>
       </c>
       <c r="L5" s="7" t="s">
-        <v>356</v>
+        <v>352</v>
       </c>
       <c r="M5" s="1"/>
       <c r="N5" s="1" t="s">
@@ -16452,7 +16426,7 @@
         <v>249</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>325</v>
+        <v>321</v>
       </c>
       <c r="F6" s="1" t="s">
         <v>5</v>
@@ -16467,7 +16441,7 @@
         <v>181</v>
       </c>
       <c r="J6" s="1" t="s">
-        <v>346</v>
+        <v>342</v>
       </c>
       <c r="K6" s="7" t="s">
         <v>190</v>
@@ -16494,16 +16468,16 @@
         <v>115</v>
       </c>
       <c r="G7" t="s">
-        <v>337</v>
+        <v>333</v>
       </c>
       <c r="H7" t="s">
-        <v>331</v>
+        <v>327</v>
       </c>
       <c r="I7" t="s">
-        <v>357</v>
+        <v>353</v>
       </c>
       <c r="J7" s="1" t="s">
-        <v>347</v>
+        <v>343</v>
       </c>
       <c r="K7" s="7" t="s">
         <v>247</v>
@@ -16533,10 +16507,10 @@
         <v>125</v>
       </c>
       <c r="H8" t="s">
-        <v>332</v>
+        <v>328</v>
       </c>
       <c r="I8" t="s">
-        <v>358</v>
+        <v>354</v>
       </c>
       <c r="J8" s="1"/>
       <c r="K8" s="7" t="s">
@@ -16567,11 +16541,11 @@
         <v>257</v>
       </c>
       <c r="I9" t="s">
-        <v>359</v>
+        <v>355</v>
       </c>
       <c r="J9" s="1"/>
       <c r="K9" s="7" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="L9" s="7"/>
       <c r="M9" s="1"/>
@@ -16598,7 +16572,7 @@
         <v>40</v>
       </c>
       <c r="H10" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="I10" t="s">
         <v>253</v>
@@ -16622,7 +16596,7 @@
         <v>174</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>305</v>
+        <v>302</v>
       </c>
       <c r="E11" s="1"/>
       <c r="F11" s="1" t="s">
@@ -16632,7 +16606,7 @@
         <v>264</v>
       </c>
       <c r="H11" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="I11" t="s">
         <v>243</v>
@@ -16656,20 +16630,20 @@
         <v>170</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>323</v>
+        <v>319</v>
       </c>
       <c r="E12" s="1"/>
       <c r="F12" s="1" t="s">
         <v>177</v>
       </c>
       <c r="G12" t="s">
-        <v>338</v>
+        <v>334</v>
       </c>
       <c r="H12" t="s">
         <v>162</v>
       </c>
       <c r="I12" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="J12" s="1"/>
       <c r="K12" s="7" t="s">
@@ -16695,7 +16669,7 @@
         <v>173</v>
       </c>
       <c r="G13" t="s">
-        <v>339</v>
+        <v>335</v>
       </c>
       <c r="H13" t="s">
         <v>157</v>
@@ -16705,7 +16679,7 @@
       </c>
       <c r="J13" s="1"/>
       <c r="K13" s="7" t="s">
-        <v>343</v>
+        <v>339</v>
       </c>
       <c r="L13" s="7"/>
       <c r="M13" s="1"/>
@@ -16759,7 +16733,7 @@
         <v>43</v>
       </c>
       <c r="G15" t="s">
-        <v>340</v>
+        <v>336</v>
       </c>
       <c r="H15" t="s">
         <v>93</v>
@@ -16794,7 +16768,7 @@
         <v>77</v>
       </c>
       <c r="H16" t="s">
-        <v>333</v>
+        <v>329</v>
       </c>
       <c r="I16" t="s">
         <v>12</v>
@@ -16881,7 +16855,7 @@
         <v>22</v>
       </c>
       <c r="G19" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="H19" t="s">
         <v>80</v>
@@ -16911,7 +16885,7 @@
         <v>151</v>
       </c>
       <c r="G20" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="H20" t="s">
         <v>79</v>
@@ -16921,7 +16895,7 @@
       </c>
       <c r="J20" s="1"/>
       <c r="K20" s="7" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="L20" s="7"/>
       <c r="M20" s="1"/>
@@ -17039,7 +17013,7 @@
       </c>
       <c r="J24" s="1"/>
       <c r="K24" s="7" t="s">
-        <v>341</v>
+        <v>337</v>
       </c>
       <c r="L24" s="7"/>
       <c r="M24" s="1"/>
@@ -17060,10 +17034,10 @@
       </c>
       <c r="G25" s="1"/>
       <c r="H25" t="s">
-        <v>334</v>
+        <v>330</v>
       </c>
       <c r="I25" t="s">
-        <v>329</v>
+        <v>325</v>
       </c>
       <c r="J25" s="1"/>
       <c r="K25" s="7" t="s">
@@ -17091,7 +17065,7 @@
       <c r="I26" s="1"/>
       <c r="J26" s="1"/>
       <c r="K26" s="7" t="s">
-        <v>300</v>
+        <v>298</v>
       </c>
       <c r="L26" s="7"/>
       <c r="M26" s="1"/>
@@ -17347,7 +17321,7 @@
       <c r="I38" s="1"/>
       <c r="J38" s="1"/>
       <c r="K38" s="7" t="s">
-        <v>344</v>
+        <v>340</v>
       </c>
       <c r="L38" s="7"/>
       <c r="M38" s="1"/>
@@ -17367,7 +17341,7 @@
       <c r="I39" s="1"/>
       <c r="J39" s="1"/>
       <c r="K39" s="7" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="L39" s="7"/>
       <c r="M39" s="1"/>
@@ -17427,7 +17401,7 @@
       <c r="I42" s="1"/>
       <c r="J42" s="1"/>
       <c r="K42" s="7" t="s">
-        <v>302</v>
+        <v>299</v>
       </c>
       <c r="L42" s="7"/>
       <c r="M42" s="1"/>
@@ -17606,7 +17580,7 @@
       <c r="I51" s="1"/>
       <c r="J51" s="1"/>
       <c r="K51" s="7" t="s">
-        <v>342</v>
+        <v>338</v>
       </c>
       <c r="L51" s="7"/>
       <c r="M51" s="1"/>
@@ -17664,7 +17638,7 @@
       <c r="I54" s="1"/>
       <c r="J54" s="1"/>
       <c r="K54" s="7" t="s">
-        <v>303</v>
+        <v>300</v>
       </c>
       <c r="L54" s="7"/>
       <c r="M54" s="1"/>
@@ -17964,7 +17938,7 @@
       <c r="I69" s="1"/>
       <c r="J69" s="1"/>
       <c r="K69" s="7" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="L69" s="7"/>
       <c r="M69" s="1"/>
@@ -17984,7 +17958,7 @@
       <c r="I70" s="1"/>
       <c r="J70" s="1"/>
       <c r="K70" s="7" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="L70" s="7"/>
       <c r="M70" s="1"/>

--- a/data/a_01_mortality_data_processed/cod_algorithm/final_kw_v1.xlsx
+++ b/data/a_01_mortality_data_processed/cod_algorithm/final_kw_v1.xlsx
@@ -8,16 +8,16 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/gabrieladaza/Documents/GitHub/harmonized_carceral_mortality_data/data/a_01_mortality_data_processed/cod_algorithm/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EAF8AB39-60E8-2D44-9C76-4FD72F38C685}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1F89E899-41C2-8449-9785-2AB43BF0F347}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="760" windowWidth="30240" windowHeight="17540" firstSheet="1" activeTab="2" xr2:uid="{A6ED5751-AE0F-B045-AA43-8F95CA62E1A7}"/>
+    <workbookView xWindow="0" yWindow="760" windowWidth="30240" windowHeight="17480" firstSheet="1" activeTab="5" xr2:uid="{A6ED5751-AE0F-B045-AA43-8F95CA62E1A7}"/>
   </bookViews>
   <sheets>
     <sheet name="sheet_names" sheetId="6" r:id="rId1"/>
     <sheet name="keywords" sheetId="2" r:id="rId2"/>
     <sheet name="additional keywords" sheetId="3" r:id="rId3"/>
-    <sheet name="keywords_additional" sheetId="4" r:id="rId4"/>
-    <sheet name="adapted_keywords" sheetId="5" r:id="rId5"/>
+    <sheet name="keywords_plus_additional" sheetId="4" r:id="rId4"/>
+    <sheet name="adapted_keyword_scheme" sheetId="5" r:id="rId5"/>
     <sheet name="kw_icd_categories" sheetId="7" r:id="rId6"/>
   </sheets>
   <calcPr calcId="191029"/>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1438" uniqueCount="356">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1440" uniqueCount="358">
   <si>
     <t>DIABETES</t>
   </si>
@@ -1109,6 +1109,12 @@
   </si>
   <si>
     <t>CEREBROVASCULAR</t>
+  </si>
+  <si>
+    <t>COVID-19 KEYWORDS</t>
+  </si>
+  <si>
+    <t>CORONAVIRUS</t>
   </si>
 </sst>
 </file>
@@ -16167,7 +16173,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DBEE812F-4599-D14A-8994-D04F411E7319}">
-  <dimension ref="A1:O355"/>
+  <dimension ref="A1:P355"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="2" width="21.5" customWidth="1"/>
@@ -16177,15 +16183,15 @@
     <col min="6" max="6" width="36" customWidth="1"/>
     <col min="7" max="7" width="36.6640625" customWidth="1"/>
     <col min="8" max="8" width="24.83203125" customWidth="1"/>
-    <col min="9" max="9" width="35.33203125" customWidth="1"/>
-    <col min="10" max="10" width="37.6640625" customWidth="1"/>
-    <col min="11" max="12" width="42.1640625" customWidth="1"/>
-    <col min="13" max="13" width="14.83203125" customWidth="1"/>
-    <col min="14" max="14" width="16.33203125" customWidth="1"/>
-    <col min="15" max="15" width="16.5" customWidth="1"/>
+    <col min="9" max="10" width="35.33203125" customWidth="1"/>
+    <col min="11" max="11" width="37.6640625" customWidth="1"/>
+    <col min="12" max="13" width="42.1640625" customWidth="1"/>
+    <col min="14" max="14" width="14.83203125" customWidth="1"/>
+    <col min="15" max="15" width="16.33203125" customWidth="1"/>
+    <col min="16" max="16" width="16.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" ht="34" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:16" ht="34" x14ac:dyDescent="0.2">
       <c r="A1" s="3" t="s">
         <v>220</v>
       </c>
@@ -16214,25 +16220,28 @@
         <v>323</v>
       </c>
       <c r="J1" s="4" t="s">
+        <v>356</v>
+      </c>
+      <c r="K1" s="4" t="s">
         <v>307</v>
       </c>
-      <c r="K1" s="6" t="s">
+      <c r="L1" s="6" t="s">
         <v>341</v>
       </c>
-      <c r="L1" s="6" t="s">
+      <c r="M1" s="6" t="s">
         <v>348</v>
       </c>
-      <c r="M1" s="3" t="s">
+      <c r="N1" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="N1" s="3" t="s">
+      <c r="O1" s="3" t="s">
         <v>221</v>
       </c>
-      <c r="O1" t="s">
+      <c r="P1" t="s">
         <v>345</v>
       </c>
     </row>
-    <row r="2" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="1" t="s">
         <v>219</v>
       </c>
@@ -16261,25 +16270,28 @@
         <v>242</v>
       </c>
       <c r="J2" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="K2" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="K2" s="7" t="s">
+      <c r="L2" s="7" t="s">
         <v>216</v>
       </c>
-      <c r="L2" s="7" t="s">
+      <c r="M2" s="7" t="s">
         <v>349</v>
       </c>
-      <c r="M2" s="1" t="s">
+      <c r="N2" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="N2" s="1" t="s">
+      <c r="O2" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="O2" t="s">
+      <c r="P2" t="s">
         <v>346</v>
       </c>
     </row>
-    <row r="3" spans="1:15" ht="16" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A3" s="1" t="s">
         <v>213</v>
       </c>
@@ -16307,26 +16319,29 @@
       <c r="I3" t="s">
         <v>244</v>
       </c>
-      <c r="J3" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="K3" s="7" t="s">
+      <c r="J3" t="s">
+        <v>357</v>
+      </c>
+      <c r="K3" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="L3" s="7" t="s">
         <v>198</v>
       </c>
-      <c r="L3" s="7" t="s">
+      <c r="M3" s="7" t="s">
         <v>350</v>
       </c>
-      <c r="M3" s="1" t="s">
+      <c r="N3" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="N3" s="1" t="s">
+      <c r="O3" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="O3" t="s">
+      <c r="P3" t="s">
         <v>347</v>
       </c>
     </row>
-    <row r="4" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A4" s="1" t="s">
         <v>207</v>
       </c>
@@ -16354,23 +16369,23 @@
       <c r="I4" t="s">
         <v>287</v>
       </c>
-      <c r="J4" s="1" t="s">
-        <v>85</v>
-      </c>
-      <c r="K4" s="7" t="s">
+      <c r="K4" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="L4" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="L4" s="7" t="s">
+      <c r="M4" s="7" t="s">
         <v>351</v>
       </c>
-      <c r="M4" s="1" t="s">
+      <c r="N4" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="N4" s="1" t="s">
+      <c r="O4" s="1" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="5" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>202</v>
       </c>
@@ -16398,21 +16413,21 @@
       <c r="I5" t="s">
         <v>187</v>
       </c>
-      <c r="J5" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="K5" s="7" t="s">
+      <c r="K5" s="1" t="s">
+        <v>342</v>
+      </c>
+      <c r="L5" s="7" t="s">
         <v>245</v>
       </c>
-      <c r="L5" s="7" t="s">
+      <c r="M5" s="7" t="s">
         <v>352</v>
       </c>
-      <c r="M5" s="1"/>
-      <c r="N5" s="1" t="s">
+      <c r="N5" s="1"/>
+      <c r="O5" s="1" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="6" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A6" s="1" t="s">
         <v>196</v>
       </c>
@@ -16440,19 +16455,19 @@
       <c r="I6" t="s">
         <v>181</v>
       </c>
-      <c r="J6" s="1" t="s">
-        <v>342</v>
-      </c>
-      <c r="K6" s="7" t="s">
+      <c r="K6" s="1" t="s">
+        <v>343</v>
+      </c>
+      <c r="L6" s="7" t="s">
         <v>190</v>
       </c>
-      <c r="L6" s="7"/>
-      <c r="M6" s="1"/>
-      <c r="N6" s="1" t="s">
+      <c r="M6" s="7"/>
+      <c r="N6" s="1"/>
+      <c r="O6" s="1" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="7" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A7" s="1" t="s">
         <v>192</v>
       </c>
@@ -16476,19 +16491,17 @@
       <c r="I7" t="s">
         <v>353</v>
       </c>
-      <c r="J7" s="1" t="s">
-        <v>343</v>
-      </c>
-      <c r="K7" s="7" t="s">
+      <c r="K7" s="1"/>
+      <c r="L7" s="7" t="s">
         <v>247</v>
       </c>
-      <c r="L7" s="7"/>
-      <c r="M7" s="1"/>
-      <c r="N7" s="1" t="s">
+      <c r="M7" s="7"/>
+      <c r="N7" s="1"/>
+      <c r="O7" s="1" t="s">
         <v>184</v>
       </c>
     </row>
-    <row r="8" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A8" s="1" t="s">
         <v>188</v>
       </c>
@@ -16512,17 +16525,17 @@
       <c r="I8" t="s">
         <v>354</v>
       </c>
-      <c r="J8" s="1"/>
-      <c r="K8" s="7" t="s">
+      <c r="K8" s="1"/>
+      <c r="L8" s="7" t="s">
         <v>273</v>
       </c>
-      <c r="L8" s="7"/>
-      <c r="M8" s="1"/>
-      <c r="N8" s="1" t="s">
+      <c r="M8" s="7"/>
+      <c r="N8" s="1"/>
+      <c r="O8" s="1" t="s">
         <v>178</v>
       </c>
     </row>
-    <row r="9" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A9" s="1" t="s">
         <v>185</v>
       </c>
@@ -16543,17 +16556,17 @@
       <c r="I9" t="s">
         <v>355</v>
       </c>
-      <c r="J9" s="1"/>
-      <c r="K9" s="7" t="s">
+      <c r="K9" s="1"/>
+      <c r="L9" s="7" t="s">
         <v>295</v>
       </c>
-      <c r="L9" s="7"/>
-      <c r="M9" s="1"/>
-      <c r="N9" s="1" t="s">
+      <c r="M9" s="7"/>
+      <c r="N9" s="1"/>
+      <c r="O9" s="1" t="s">
         <v>167</v>
       </c>
     </row>
-    <row r="10" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A10" s="1" t="s">
         <v>179</v>
       </c>
@@ -16577,17 +16590,17 @@
       <c r="I10" t="s">
         <v>253</v>
       </c>
-      <c r="J10" s="1"/>
-      <c r="K10" s="7" t="s">
+      <c r="K10" s="1"/>
+      <c r="L10" s="7" t="s">
         <v>63</v>
       </c>
-      <c r="L10" s="7"/>
-      <c r="M10" s="1"/>
-      <c r="N10" s="1" t="s">
+      <c r="M10" s="7"/>
+      <c r="N10" s="1"/>
+      <c r="O10" s="1" t="s">
         <v>53</v>
       </c>
     </row>
-    <row r="11" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A11" s="1" t="s">
         <v>176</v>
       </c>
@@ -16611,17 +16624,17 @@
       <c r="I11" t="s">
         <v>243</v>
       </c>
-      <c r="J11" s="1"/>
-      <c r="K11" s="7" t="s">
+      <c r="K11" s="1"/>
+      <c r="L11" s="7" t="s">
         <v>27</v>
       </c>
-      <c r="L11" s="7"/>
-      <c r="M11" s="1"/>
-      <c r="N11" s="1" t="s">
+      <c r="M11" s="7"/>
+      <c r="N11" s="1"/>
+      <c r="O11" s="1" t="s">
         <v>160</v>
       </c>
     </row>
-    <row r="12" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A12" s="1" t="s">
         <v>86</v>
       </c>
@@ -16645,17 +16658,17 @@
       <c r="I12" t="s">
         <v>281</v>
       </c>
-      <c r="J12" s="1"/>
-      <c r="K12" s="7" t="s">
+      <c r="K12" s="1"/>
+      <c r="L12" s="7" t="s">
         <v>35</v>
       </c>
-      <c r="L12" s="7"/>
-      <c r="M12" s="1"/>
-      <c r="N12" s="1" t="s">
+      <c r="M12" s="7"/>
+      <c r="N12" s="1"/>
+      <c r="O12" s="1" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="13" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A13" s="1" t="s">
         <v>172</v>
       </c>
@@ -16677,17 +16690,17 @@
       <c r="I13" t="s">
         <v>58</v>
       </c>
-      <c r="J13" s="1"/>
-      <c r="K13" s="7" t="s">
+      <c r="K13" s="1"/>
+      <c r="L13" s="7" t="s">
         <v>339</v>
       </c>
-      <c r="L13" s="7"/>
-      <c r="M13" s="1"/>
-      <c r="N13" s="1" t="s">
+      <c r="M13" s="7"/>
+      <c r="N13" s="1"/>
+      <c r="O13" s="1" t="s">
         <v>146</v>
       </c>
     </row>
-    <row r="14" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A14" s="1" t="s">
         <v>168</v>
       </c>
@@ -16709,17 +16722,17 @@
       <c r="I14" t="s">
         <v>59</v>
       </c>
-      <c r="J14" s="1"/>
-      <c r="K14" s="7" t="s">
+      <c r="K14" s="1"/>
+      <c r="L14" s="7" t="s">
         <v>36</v>
       </c>
-      <c r="L14" s="7"/>
-      <c r="M14" s="1"/>
-      <c r="N14" s="1" t="s">
+      <c r="M14" s="7"/>
+      <c r="N14" s="1"/>
+      <c r="O14" s="1" t="s">
         <v>142</v>
       </c>
     </row>
-    <row r="15" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A15" s="1" t="s">
         <v>165</v>
       </c>
@@ -16741,17 +16754,17 @@
       <c r="I15" t="s">
         <v>87</v>
       </c>
-      <c r="J15" s="1"/>
-      <c r="K15" s="7" t="s">
+      <c r="K15" s="1"/>
+      <c r="L15" s="7" t="s">
         <v>139</v>
       </c>
-      <c r="L15" s="7"/>
-      <c r="M15" s="1"/>
-      <c r="N15" s="1" t="s">
+      <c r="M15" s="7"/>
+      <c r="N15" s="1"/>
+      <c r="O15" s="1" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="16" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A16" s="1" t="s">
         <v>161</v>
       </c>
@@ -16773,17 +16786,17 @@
       <c r="I16" t="s">
         <v>12</v>
       </c>
-      <c r="J16" s="1"/>
-      <c r="K16" s="7" t="s">
+      <c r="K16" s="1"/>
+      <c r="L16" s="7" t="s">
         <v>135</v>
       </c>
-      <c r="L16" s="7"/>
-      <c r="M16" s="1"/>
-      <c r="N16" s="1" t="s">
+      <c r="M16" s="7"/>
+      <c r="N16" s="1"/>
+      <c r="O16" s="1" t="s">
         <v>137</v>
       </c>
     </row>
-    <row r="17" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A17" s="1" t="s">
         <v>156</v>
       </c>
@@ -16803,17 +16816,17 @@
       <c r="I17" t="s">
         <v>266</v>
       </c>
-      <c r="J17" s="1"/>
-      <c r="K17" s="7" t="s">
+      <c r="K17" s="1"/>
+      <c r="L17" s="7" t="s">
         <v>49</v>
       </c>
-      <c r="L17" s="7"/>
-      <c r="M17" s="1"/>
-      <c r="N17" s="1" t="s">
+      <c r="M17" s="7"/>
+      <c r="N17" s="1"/>
+      <c r="O17" s="1" t="s">
         <v>133</v>
       </c>
     </row>
-    <row r="18" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A18" s="1" t="s">
         <v>154</v>
       </c>
@@ -16833,17 +16846,17 @@
       <c r="I18" t="s">
         <v>265</v>
       </c>
-      <c r="J18" s="1"/>
-      <c r="K18" s="7" t="s">
+      <c r="K18" s="1"/>
+      <c r="L18" s="7" t="s">
         <v>122</v>
       </c>
-      <c r="L18" s="7"/>
-      <c r="M18" s="1"/>
-      <c r="N18" s="1" t="s">
+      <c r="M18" s="7"/>
+      <c r="N18" s="1"/>
+      <c r="O18" s="1" t="s">
         <v>131</v>
       </c>
     </row>
-    <row r="19" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A19" s="1" t="s">
         <v>153</v>
       </c>
@@ -16863,17 +16876,17 @@
       <c r="I19" t="s">
         <v>44</v>
       </c>
-      <c r="J19" s="1"/>
-      <c r="K19" s="7" t="s">
+      <c r="K19" s="1"/>
+      <c r="L19" s="7" t="s">
         <v>39</v>
       </c>
-      <c r="L19" s="7"/>
-      <c r="M19" s="1"/>
-      <c r="N19" s="1" t="s">
+      <c r="M19" s="7"/>
+      <c r="N19" s="1"/>
+      <c r="O19" s="1" t="s">
         <v>127</v>
       </c>
     </row>
-    <row r="20" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A20" s="1" t="s">
         <v>45</v>
       </c>
@@ -16893,17 +16906,17 @@
       <c r="I20" t="s">
         <v>65</v>
       </c>
-      <c r="J20" s="1"/>
-      <c r="K20" s="7" t="s">
+      <c r="K20" s="1"/>
+      <c r="L20" s="7" t="s">
         <v>284</v>
       </c>
-      <c r="L20" s="7"/>
-      <c r="M20" s="1"/>
-      <c r="N20" s="1" t="s">
+      <c r="M20" s="7"/>
+      <c r="N20" s="1"/>
+      <c r="O20" s="1" t="s">
         <v>144</v>
       </c>
     </row>
-    <row r="21" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A21" s="1" t="s">
         <v>147</v>
       </c>
@@ -16923,17 +16936,17 @@
       <c r="I21" t="s">
         <v>75</v>
       </c>
-      <c r="J21" s="1"/>
-      <c r="K21" s="7" t="s">
+      <c r="K21" s="1"/>
+      <c r="L21" s="7" t="s">
         <v>117</v>
       </c>
-      <c r="L21" s="7"/>
-      <c r="M21" s="1"/>
-      <c r="N21" s="1" t="s">
+      <c r="M21" s="7"/>
+      <c r="N21" s="1"/>
+      <c r="O21" s="1" t="s">
         <v>212</v>
       </c>
     </row>
-    <row r="22" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A22" s="1" t="s">
         <v>143</v>
       </c>
@@ -16953,17 +16966,17 @@
       <c r="I22" t="s">
         <v>57</v>
       </c>
-      <c r="J22" s="1"/>
-      <c r="K22" s="7" t="s">
+      <c r="K22" s="1"/>
+      <c r="L22" s="7" t="s">
         <v>0</v>
       </c>
-      <c r="L22" s="7"/>
-      <c r="M22" s="1"/>
-      <c r="N22" s="1" t="s">
+      <c r="M22" s="7"/>
+      <c r="N22" s="1"/>
+      <c r="O22" s="1" t="s">
         <v>206</v>
       </c>
     </row>
-    <row r="23" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A23" s="1" t="s">
         <v>140</v>
       </c>
@@ -16983,17 +16996,17 @@
       <c r="I23" t="s">
         <v>60</v>
       </c>
-      <c r="J23" s="1"/>
-      <c r="K23" s="7" t="s">
+      <c r="K23" s="1"/>
+      <c r="L23" s="7" t="s">
         <v>112</v>
       </c>
-      <c r="L23" s="7"/>
-      <c r="M23" s="1"/>
-      <c r="N23" s="1" t="s">
+      <c r="M23" s="7"/>
+      <c r="N23" s="1"/>
+      <c r="O23" s="1" t="s">
         <v>146</v>
       </c>
     </row>
-    <row r="24" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A24" s="1" t="s">
         <v>138</v>
       </c>
@@ -17011,17 +17024,17 @@
       <c r="I24" t="s">
         <v>26</v>
       </c>
-      <c r="J24" s="1"/>
-      <c r="K24" s="7" t="s">
+      <c r="K24" s="1"/>
+      <c r="L24" s="7" t="s">
         <v>337</v>
       </c>
-      <c r="L24" s="7"/>
-      <c r="M24" s="1"/>
-      <c r="N24" s="1" t="s">
+      <c r="M24" s="7"/>
+      <c r="N24" s="1"/>
+      <c r="O24" s="1" t="s">
         <v>142</v>
       </c>
     </row>
-    <row r="25" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A25" s="1" t="s">
         <v>134</v>
       </c>
@@ -17039,17 +17052,17 @@
       <c r="I25" t="s">
         <v>325</v>
       </c>
-      <c r="J25" s="1"/>
-      <c r="K25" s="7" t="s">
+      <c r="K25" s="1"/>
+      <c r="L25" s="7" t="s">
         <v>110</v>
       </c>
-      <c r="L25" s="7"/>
-      <c r="M25" s="1"/>
-      <c r="N25" s="1" t="s">
+      <c r="M25" s="7"/>
+      <c r="N25" s="1"/>
+      <c r="O25" s="1" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="26" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A26" s="1" t="s">
         <v>132</v>
       </c>
@@ -17064,16 +17077,17 @@
       <c r="H26" s="1"/>
       <c r="I26" s="1"/>
       <c r="J26" s="1"/>
-      <c r="K26" s="7" t="s">
+      <c r="K26" s="1"/>
+      <c r="L26" s="7" t="s">
         <v>298</v>
       </c>
-      <c r="L26" s="7"/>
-      <c r="M26" s="1"/>
-      <c r="N26" s="1" t="s">
+      <c r="M26" s="7"/>
+      <c r="N26" s="1"/>
+      <c r="O26" s="1" t="s">
         <v>137</v>
       </c>
     </row>
-    <row r="27" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A27" s="1" t="s">
         <v>128</v>
       </c>
@@ -17088,16 +17102,17 @@
       <c r="H27" s="1"/>
       <c r="I27" s="1"/>
       <c r="J27" s="1"/>
-      <c r="K27" s="7" t="s">
+      <c r="K27" s="1"/>
+      <c r="L27" s="7" t="s">
         <v>55</v>
       </c>
-      <c r="L27" s="7"/>
-      <c r="M27" s="1"/>
-      <c r="N27" s="1" t="s">
+      <c r="M27" s="7"/>
+      <c r="N27" s="1"/>
+      <c r="O27" s="1" t="s">
         <v>133</v>
       </c>
     </row>
-    <row r="28" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A28" s="1" t="s">
         <v>124</v>
       </c>
@@ -17111,16 +17126,17 @@
       <c r="H28" s="1"/>
       <c r="I28" s="1"/>
       <c r="J28" s="1"/>
-      <c r="K28" s="7" t="s">
+      <c r="K28" s="1"/>
+      <c r="L28" s="7" t="s">
         <v>106</v>
       </c>
-      <c r="L28" s="7"/>
-      <c r="M28" s="1"/>
-      <c r="N28" s="1" t="s">
+      <c r="M28" s="7"/>
+      <c r="N28" s="1"/>
+      <c r="O28" s="1" t="s">
         <v>131</v>
       </c>
     </row>
-    <row r="29" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A29" s="1" t="s">
         <v>121</v>
       </c>
@@ -17134,16 +17150,17 @@
       <c r="H29" s="1"/>
       <c r="I29" s="1"/>
       <c r="J29" s="1"/>
-      <c r="K29" s="7" t="s">
+      <c r="K29" s="1"/>
+      <c r="L29" s="7" t="s">
         <v>267</v>
       </c>
-      <c r="L29" s="7"/>
-      <c r="M29" s="1"/>
-      <c r="N29" s="1" t="s">
+      <c r="M29" s="7"/>
+      <c r="N29" s="1"/>
+      <c r="O29" s="1" t="s">
         <v>127</v>
       </c>
     </row>
-    <row r="30" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A30" s="1" t="s">
         <v>119</v>
       </c>
@@ -17157,16 +17174,17 @@
       <c r="H30" s="1"/>
       <c r="I30" s="1"/>
       <c r="J30" s="1"/>
-      <c r="K30" s="7" t="s">
+      <c r="K30" s="1"/>
+      <c r="L30" s="7" t="s">
         <v>104</v>
       </c>
-      <c r="L30" s="7"/>
-      <c r="M30" s="1"/>
-      <c r="N30" s="1" t="s">
+      <c r="M30" s="7"/>
+      <c r="N30" s="1"/>
+      <c r="O30" s="1" t="s">
         <v>175</v>
       </c>
     </row>
-    <row r="31" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A31" s="1" t="s">
         <v>118</v>
       </c>
@@ -17180,14 +17198,15 @@
       <c r="H31" s="1"/>
       <c r="I31" s="1"/>
       <c r="J31" s="1"/>
-      <c r="K31" s="7" t="s">
+      <c r="K31" s="1"/>
+      <c r="L31" s="7" t="s">
         <v>102</v>
       </c>
-      <c r="L31" s="7"/>
-      <c r="M31" s="1"/>
+      <c r="M31" s="7"/>
       <c r="N31" s="1"/>
-    </row>
-    <row r="32" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O31" s="1"/>
+    </row>
+    <row r="32" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A32" s="1" t="s">
         <v>116</v>
       </c>
@@ -17201,14 +17220,15 @@
       <c r="H32" s="1"/>
       <c r="I32" s="1"/>
       <c r="J32" s="1"/>
-      <c r="K32" s="7" t="s">
+      <c r="K32" s="1"/>
+      <c r="L32" s="7" t="s">
         <v>100</v>
       </c>
-      <c r="L32" s="7"/>
-      <c r="M32" s="1"/>
+      <c r="M32" s="7"/>
       <c r="N32" s="1"/>
-    </row>
-    <row r="33" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O32" s="1"/>
+    </row>
+    <row r="33" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A33" s="1" t="s">
         <v>114</v>
       </c>
@@ -17220,14 +17240,15 @@
       <c r="H33" s="1"/>
       <c r="I33" s="1"/>
       <c r="J33" s="1"/>
-      <c r="K33" s="7" t="s">
+      <c r="K33" s="1"/>
+      <c r="L33" s="7" t="s">
         <v>37</v>
       </c>
-      <c r="L33" s="7"/>
-      <c r="M33" s="1"/>
+      <c r="M33" s="7"/>
       <c r="N33" s="1"/>
-    </row>
-    <row r="34" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O33" s="1"/>
+    </row>
+    <row r="34" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A34" s="1" t="s">
         <v>111</v>
       </c>
@@ -17240,14 +17261,15 @@
       <c r="H34" s="1"/>
       <c r="I34" s="1"/>
       <c r="J34" s="1"/>
-      <c r="K34" s="7" t="s">
+      <c r="K34" s="1"/>
+      <c r="L34" s="7" t="s">
         <v>97</v>
       </c>
-      <c r="L34" s="7"/>
-      <c r="M34" s="1"/>
+      <c r="M34" s="7"/>
       <c r="N34" s="1"/>
-    </row>
-    <row r="35" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O34" s="1"/>
+    </row>
+    <row r="35" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A35" s="1" t="s">
         <v>109</v>
       </c>
@@ -17260,14 +17282,15 @@
       <c r="H35" s="1"/>
       <c r="I35" s="1"/>
       <c r="J35" s="1"/>
-      <c r="K35" s="7" t="s">
+      <c r="K35" s="1"/>
+      <c r="L35" s="7" t="s">
         <v>274</v>
       </c>
-      <c r="L35" s="7"/>
-      <c r="M35" s="1"/>
+      <c r="M35" s="7"/>
       <c r="N35" s="1"/>
-    </row>
-    <row r="36" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O35" s="1"/>
+    </row>
+    <row r="36" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A36" s="1" t="s">
         <v>108</v>
       </c>
@@ -17280,14 +17303,15 @@
       <c r="H36" s="1"/>
       <c r="I36" s="1"/>
       <c r="J36" s="1"/>
-      <c r="K36" s="7" t="s">
+      <c r="K36" s="1"/>
+      <c r="L36" s="7" t="s">
         <v>95</v>
       </c>
-      <c r="L36" s="7"/>
-      <c r="M36" s="1"/>
+      <c r="M36" s="7"/>
       <c r="N36" s="1"/>
-    </row>
-    <row r="37" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O36" s="1"/>
+    </row>
+    <row r="37" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A37" s="1" t="s">
         <v>107</v>
       </c>
@@ -17300,14 +17324,15 @@
       <c r="H37" s="1"/>
       <c r="I37" s="1"/>
       <c r="J37" s="1"/>
-      <c r="K37" s="7" t="s">
+      <c r="K37" s="1"/>
+      <c r="L37" s="7" t="s">
         <v>268</v>
       </c>
-      <c r="L37" s="7"/>
-      <c r="M37" s="1"/>
+      <c r="M37" s="7"/>
       <c r="N37" s="1"/>
-    </row>
-    <row r="38" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O37" s="1"/>
+    </row>
+    <row r="38" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A38" s="1" t="s">
         <v>105</v>
       </c>
@@ -17320,14 +17345,15 @@
       <c r="H38" s="1"/>
       <c r="I38" s="1"/>
       <c r="J38" s="1"/>
-      <c r="K38" s="7" t="s">
+      <c r="K38" s="1"/>
+      <c r="L38" s="7" t="s">
         <v>340</v>
       </c>
-      <c r="L38" s="7"/>
-      <c r="M38" s="1"/>
+      <c r="M38" s="7"/>
       <c r="N38" s="1"/>
-    </row>
-    <row r="39" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O38" s="1"/>
+    </row>
+    <row r="39" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A39" s="1" t="s">
         <v>227</v>
       </c>
@@ -17340,14 +17366,15 @@
       <c r="H39" s="1"/>
       <c r="I39" s="1"/>
       <c r="J39" s="1"/>
-      <c r="K39" s="7" t="s">
+      <c r="K39" s="1"/>
+      <c r="L39" s="7" t="s">
         <v>282</v>
       </c>
-      <c r="L39" s="7"/>
-      <c r="M39" s="1"/>
+      <c r="M39" s="7"/>
       <c r="N39" s="1"/>
-    </row>
-    <row r="40" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O39" s="1"/>
+    </row>
+    <row r="40" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A40" s="1" t="s">
         <v>88</v>
       </c>
@@ -17360,14 +17387,15 @@
       <c r="H40" s="1"/>
       <c r="I40" s="1"/>
       <c r="J40" s="1"/>
-      <c r="K40" s="7" t="s">
+      <c r="K40" s="1"/>
+      <c r="L40" s="7" t="s">
         <v>33</v>
       </c>
-      <c r="L40" s="7"/>
-      <c r="M40" s="1"/>
+      <c r="M40" s="7"/>
       <c r="N40" s="1"/>
-    </row>
-    <row r="41" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O40" s="1"/>
+    </row>
+    <row r="41" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A41" s="1" t="s">
         <v>103</v>
       </c>
@@ -17380,14 +17408,15 @@
       <c r="H41" s="1"/>
       <c r="I41" s="1"/>
       <c r="J41" s="1"/>
-      <c r="K41" s="7" t="s">
+      <c r="K41" s="1"/>
+      <c r="L41" s="7" t="s">
         <v>89</v>
       </c>
-      <c r="L41" s="7"/>
-      <c r="M41" s="1"/>
+      <c r="M41" s="7"/>
       <c r="N41" s="1"/>
-    </row>
-    <row r="42" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O41" s="1"/>
+    </row>
+    <row r="42" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A42" s="1" t="s">
         <v>101</v>
       </c>
@@ -17400,14 +17429,15 @@
       <c r="H42" s="1"/>
       <c r="I42" s="1"/>
       <c r="J42" s="1"/>
-      <c r="K42" s="7" t="s">
+      <c r="K42" s="1"/>
+      <c r="L42" s="7" t="s">
         <v>299</v>
       </c>
-      <c r="L42" s="7"/>
-      <c r="M42" s="1"/>
+      <c r="M42" s="7"/>
       <c r="N42" s="1"/>
-    </row>
-    <row r="43" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O42" s="1"/>
+    </row>
+    <row r="43" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A43" s="1" t="s">
         <v>99</v>
       </c>
@@ -17420,14 +17450,15 @@
       <c r="H43" s="1"/>
       <c r="I43" s="1"/>
       <c r="J43" s="1"/>
-      <c r="K43" s="7" t="s">
+      <c r="K43" s="1"/>
+      <c r="L43" s="7" t="s">
         <v>17</v>
       </c>
-      <c r="L43" s="7"/>
-      <c r="M43" s="1"/>
+      <c r="M43" s="7"/>
       <c r="N43" s="1"/>
-    </row>
-    <row r="44" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O43" s="1"/>
+    </row>
+    <row r="44" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A44" s="1" t="s">
         <v>98</v>
       </c>
@@ -17440,14 +17471,15 @@
       <c r="H44" s="1"/>
       <c r="I44" s="1"/>
       <c r="J44" s="1"/>
-      <c r="K44" s="7" t="s">
+      <c r="K44" s="1"/>
+      <c r="L44" s="7" t="s">
         <v>256</v>
       </c>
-      <c r="L44" s="7"/>
-      <c r="M44" s="1"/>
+      <c r="M44" s="7"/>
       <c r="N44" s="1"/>
-    </row>
-    <row r="45" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O44" s="1"/>
+    </row>
+    <row r="45" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A45" s="1" t="s">
         <v>96</v>
       </c>
@@ -17460,14 +17492,15 @@
       <c r="H45" s="1"/>
       <c r="I45" s="1"/>
       <c r="J45" s="1"/>
-      <c r="K45" s="7" t="s">
+      <c r="K45" s="1"/>
+      <c r="L45" s="7" t="s">
         <v>66</v>
       </c>
-      <c r="L45" s="7"/>
-      <c r="M45" s="1"/>
+      <c r="M45" s="7"/>
       <c r="N45" s="1"/>
-    </row>
-    <row r="46" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O45" s="1"/>
+    </row>
+    <row r="46" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A46" s="1" t="s">
         <v>94</v>
       </c>
@@ -17480,14 +17513,15 @@
       <c r="H46" s="1"/>
       <c r="I46" s="1"/>
       <c r="J46" s="1"/>
-      <c r="K46" s="7" t="s">
+      <c r="K46" s="1"/>
+      <c r="L46" s="7" t="s">
         <v>84</v>
       </c>
-      <c r="L46" s="7"/>
-      <c r="M46" s="1"/>
+      <c r="M46" s="7"/>
       <c r="N46" s="1"/>
-    </row>
-    <row r="47" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O46" s="1"/>
+    </row>
+    <row r="47" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A47" s="1" t="s">
         <v>92</v>
       </c>
@@ -17500,14 +17534,15 @@
       <c r="H47" s="1"/>
       <c r="I47" s="1"/>
       <c r="J47" s="1"/>
-      <c r="K47" s="7" t="s">
+      <c r="K47" s="1"/>
+      <c r="L47" s="7" t="s">
         <v>48</v>
       </c>
-      <c r="L47" s="7"/>
-      <c r="M47" s="1"/>
+      <c r="M47" s="7"/>
       <c r="N47" s="1"/>
-    </row>
-    <row r="48" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O47" s="1"/>
+    </row>
+    <row r="48" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A48" s="1" t="s">
         <v>91</v>
       </c>
@@ -17520,14 +17555,15 @@
       <c r="H48" s="1"/>
       <c r="I48" s="1"/>
       <c r="J48" s="1"/>
-      <c r="K48" s="7" t="s">
+      <c r="K48" s="1"/>
+      <c r="L48" s="7" t="s">
         <v>83</v>
       </c>
-      <c r="L48" s="7"/>
-      <c r="M48" s="1"/>
+      <c r="M48" s="7"/>
       <c r="N48" s="1"/>
-    </row>
-    <row r="49" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O48" s="1"/>
+    </row>
+    <row r="49" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A49" s="1" t="s">
         <v>90</v>
       </c>
@@ -17540,14 +17576,15 @@
       <c r="H49" s="1"/>
       <c r="I49" s="1"/>
       <c r="J49" s="1"/>
-      <c r="K49" s="7" t="s">
+      <c r="K49" s="1"/>
+      <c r="L49" s="7" t="s">
         <v>82</v>
       </c>
-      <c r="L49" s="7"/>
-      <c r="M49" s="1"/>
+      <c r="M49" s="7"/>
       <c r="N49" s="1"/>
-    </row>
-    <row r="50" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O49" s="1"/>
+    </row>
+    <row r="50" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A50" s="1" t="s">
         <v>229</v>
       </c>
@@ -17560,14 +17597,15 @@
       <c r="H50" s="1"/>
       <c r="I50" s="1"/>
       <c r="J50" s="1"/>
-      <c r="K50" s="7" t="s">
+      <c r="K50" s="1"/>
+      <c r="L50" s="7" t="s">
         <v>81</v>
       </c>
-      <c r="L50" s="7"/>
-      <c r="M50" s="1"/>
+      <c r="M50" s="7"/>
       <c r="N50" s="1"/>
-    </row>
-    <row r="51" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O50" s="1"/>
+    </row>
+    <row r="51" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A51" t="s">
         <v>234</v>
       </c>
@@ -17579,14 +17617,15 @@
       <c r="H51" s="1"/>
       <c r="I51" s="1"/>
       <c r="J51" s="1"/>
-      <c r="K51" s="7" t="s">
+      <c r="K51" s="1"/>
+      <c r="L51" s="7" t="s">
         <v>338</v>
       </c>
-      <c r="L51" s="7"/>
-      <c r="M51" s="1"/>
+      <c r="M51" s="7"/>
       <c r="N51" s="1"/>
-    </row>
-    <row r="52" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O51" s="1"/>
+    </row>
+    <row r="52" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A52" s="1" t="s">
         <v>235</v>
       </c>
@@ -17599,14 +17638,15 @@
       <c r="H52" s="1"/>
       <c r="I52" s="1"/>
       <c r="J52" s="1"/>
-      <c r="K52" s="7" t="s">
+      <c r="K52" s="1"/>
+      <c r="L52" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="L52" s="7"/>
-      <c r="M52" s="1"/>
+      <c r="M52" s="7"/>
       <c r="N52" s="1"/>
-    </row>
-    <row r="53" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O52" s="1"/>
+    </row>
+    <row r="53" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A53" t="s">
         <v>236</v>
       </c>
@@ -17618,14 +17658,15 @@
       <c r="H53" s="1"/>
       <c r="I53" s="1"/>
       <c r="J53" s="1"/>
-      <c r="K53" s="7" t="s">
+      <c r="K53" s="1"/>
+      <c r="L53" s="7" t="s">
         <v>78</v>
       </c>
-      <c r="L53" s="7"/>
-      <c r="M53" s="1"/>
+      <c r="M53" s="7"/>
       <c r="N53" s="1"/>
-    </row>
-    <row r="54" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O53" s="1"/>
+    </row>
+    <row r="54" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A54" t="s">
         <v>241</v>
       </c>
@@ -17637,14 +17678,15 @@
       <c r="H54" s="1"/>
       <c r="I54" s="1"/>
       <c r="J54" s="1"/>
-      <c r="K54" s="7" t="s">
+      <c r="K54" s="1"/>
+      <c r="L54" s="7" t="s">
         <v>300</v>
       </c>
-      <c r="L54" s="7"/>
-      <c r="M54" s="1"/>
+      <c r="M54" s="7"/>
       <c r="N54" s="1"/>
-    </row>
-    <row r="55" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O54" s="1"/>
+    </row>
+    <row r="55" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A55" s="1" t="s">
         <v>219</v>
       </c>
@@ -17657,14 +17699,15 @@
       <c r="H55" s="1"/>
       <c r="I55" s="1"/>
       <c r="J55" s="1"/>
-      <c r="K55" s="7" t="s">
+      <c r="K55" s="1"/>
+      <c r="L55" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="L55" s="7"/>
-      <c r="M55" s="1"/>
+      <c r="M55" s="7"/>
       <c r="N55" s="1"/>
-    </row>
-    <row r="56" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O55" s="1"/>
+    </row>
+    <row r="56" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A56" s="1" t="s">
         <v>213</v>
       </c>
@@ -17677,14 +17720,15 @@
       <c r="H56" s="1"/>
       <c r="I56" s="1"/>
       <c r="J56" s="1"/>
-      <c r="K56" s="7" t="s">
+      <c r="K56" s="1"/>
+      <c r="L56" s="7" t="s">
         <v>30</v>
       </c>
-      <c r="L56" s="7"/>
-      <c r="M56" s="1"/>
+      <c r="M56" s="7"/>
       <c r="N56" s="1"/>
-    </row>
-    <row r="57" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O56" s="1"/>
+    </row>
+    <row r="57" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A57" s="1" t="s">
         <v>188</v>
       </c>
@@ -17697,14 +17741,15 @@
       <c r="H57" s="1"/>
       <c r="I57" s="1"/>
       <c r="J57" s="1"/>
-      <c r="K57" s="7" t="s">
+      <c r="K57" s="1"/>
+      <c r="L57" s="7" t="s">
         <v>32</v>
       </c>
-      <c r="L57" s="7"/>
-      <c r="M57" s="1"/>
+      <c r="M57" s="7"/>
       <c r="N57" s="1"/>
-    </row>
-    <row r="58" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O57" s="1"/>
+    </row>
+    <row r="58" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A58" s="1" t="s">
         <v>185</v>
       </c>
@@ -17717,14 +17762,15 @@
       <c r="H58" s="1"/>
       <c r="I58" s="1"/>
       <c r="J58" s="1"/>
-      <c r="K58" s="7" t="s">
+      <c r="K58" s="1"/>
+      <c r="L58" s="7" t="s">
         <v>52</v>
       </c>
-      <c r="L58" s="7"/>
-      <c r="M58" s="1"/>
+      <c r="M58" s="7"/>
       <c r="N58" s="1"/>
-    </row>
-    <row r="59" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O58" s="1"/>
+    </row>
+    <row r="59" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A59" s="1" t="s">
         <v>179</v>
       </c>
@@ -17737,14 +17783,15 @@
       <c r="H59" s="1"/>
       <c r="I59" s="1"/>
       <c r="J59" s="1"/>
-      <c r="K59" s="7" t="s">
+      <c r="K59" s="1"/>
+      <c r="L59" s="7" t="s">
         <v>64</v>
       </c>
-      <c r="L59" s="7"/>
-      <c r="M59" s="1"/>
+      <c r="M59" s="7"/>
       <c r="N59" s="1"/>
-    </row>
-    <row r="60" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O59" s="1"/>
+    </row>
+    <row r="60" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A60" s="1" t="s">
         <v>176</v>
       </c>
@@ -17757,14 +17804,15 @@
       <c r="H60" s="1"/>
       <c r="I60" s="1"/>
       <c r="J60" s="1"/>
-      <c r="K60" s="7" t="s">
+      <c r="K60" s="1"/>
+      <c r="L60" s="7" t="s">
         <v>7</v>
       </c>
-      <c r="L60" s="7"/>
-      <c r="M60" s="1"/>
+      <c r="M60" s="7"/>
       <c r="N60" s="1"/>
-    </row>
-    <row r="61" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O60" s="1"/>
+    </row>
+    <row r="61" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A61" s="1" t="s">
         <v>86</v>
       </c>
@@ -17777,14 +17825,15 @@
       <c r="H61" s="1"/>
       <c r="I61" s="1"/>
       <c r="J61" s="1"/>
-      <c r="K61" s="7" t="s">
+      <c r="K61" s="1"/>
+      <c r="L61" s="7" t="s">
         <v>20</v>
       </c>
-      <c r="L61" s="7"/>
-      <c r="M61" s="1"/>
+      <c r="M61" s="7"/>
       <c r="N61" s="1"/>
-    </row>
-    <row r="62" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O61" s="1"/>
+    </row>
+    <row r="62" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A62" s="1" t="s">
         <v>172</v>
       </c>
@@ -17797,14 +17846,15 @@
       <c r="H62" s="1"/>
       <c r="I62" s="1"/>
       <c r="J62" s="1"/>
-      <c r="K62" s="7" t="s">
+      <c r="K62" s="1"/>
+      <c r="L62" s="7" t="s">
         <v>74</v>
       </c>
-      <c r="L62" s="7"/>
-      <c r="M62" s="1"/>
+      <c r="M62" s="7"/>
       <c r="N62" s="1"/>
-    </row>
-    <row r="63" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O62" s="1"/>
+    </row>
+    <row r="63" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A63" s="1" t="s">
         <v>168</v>
       </c>
@@ -17817,14 +17867,15 @@
       <c r="H63" s="1"/>
       <c r="I63" s="1"/>
       <c r="J63" s="1"/>
-      <c r="K63" s="7" t="s">
+      <c r="K63" s="1"/>
+      <c r="L63" s="7" t="s">
         <v>73</v>
       </c>
-      <c r="L63" s="7"/>
-      <c r="M63" s="1"/>
+      <c r="M63" s="7"/>
       <c r="N63" s="1"/>
-    </row>
-    <row r="64" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O63" s="1"/>
+    </row>
+    <row r="64" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A64" s="1" t="s">
         <v>165</v>
       </c>
@@ -17837,14 +17888,15 @@
       <c r="H64" s="1"/>
       <c r="I64" s="1"/>
       <c r="J64" s="1"/>
-      <c r="K64" s="7" t="s">
+      <c r="K64" s="1"/>
+      <c r="L64" s="7" t="s">
         <v>72</v>
       </c>
-      <c r="L64" s="7"/>
-      <c r="M64" s="1"/>
+      <c r="M64" s="7"/>
       <c r="N64" s="1"/>
-    </row>
-    <row r="65" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O64" s="1"/>
+    </row>
+    <row r="65" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A65" s="1" t="s">
         <v>161</v>
       </c>
@@ -17857,14 +17909,15 @@
       <c r="H65" s="1"/>
       <c r="I65" s="1"/>
       <c r="J65" s="1"/>
-      <c r="K65" s="7" t="s">
+      <c r="K65" s="1"/>
+      <c r="L65" s="7" t="s">
         <v>62</v>
       </c>
-      <c r="L65" s="7"/>
-      <c r="M65" s="1"/>
+      <c r="M65" s="7"/>
       <c r="N65" s="1"/>
-    </row>
-    <row r="66" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O65" s="1"/>
+    </row>
+    <row r="66" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A66" s="1" t="s">
         <v>156</v>
       </c>
@@ -17877,14 +17930,15 @@
       <c r="H66" s="1"/>
       <c r="I66" s="1"/>
       <c r="J66" s="1"/>
-      <c r="K66" s="7" t="s">
+      <c r="K66" s="1"/>
+      <c r="L66" s="7" t="s">
         <v>71</v>
       </c>
-      <c r="L66" s="7"/>
-      <c r="M66" s="1"/>
+      <c r="M66" s="7"/>
       <c r="N66" s="1"/>
-    </row>
-    <row r="67" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O66" s="1"/>
+    </row>
+    <row r="67" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A67" s="1" t="s">
         <v>154</v>
       </c>
@@ -17897,14 +17951,15 @@
       <c r="H67" s="1"/>
       <c r="I67" s="1"/>
       <c r="J67" s="1"/>
-      <c r="K67" s="7" t="s">
+      <c r="K67" s="1"/>
+      <c r="L67" s="7" t="s">
         <v>70</v>
       </c>
-      <c r="L67" s="7"/>
-      <c r="M67" s="1"/>
+      <c r="M67" s="7"/>
       <c r="N67" s="1"/>
-    </row>
-    <row r="68" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O67" s="1"/>
+    </row>
+    <row r="68" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A68" s="1" t="s">
         <v>153</v>
       </c>
@@ -17917,14 +17972,15 @@
       <c r="H68" s="1"/>
       <c r="I68" s="1"/>
       <c r="J68" s="1"/>
-      <c r="K68" s="7" t="s">
+      <c r="K68" s="1"/>
+      <c r="L68" s="7" t="s">
         <v>67</v>
       </c>
-      <c r="L68" s="7"/>
-      <c r="M68" s="1"/>
+      <c r="M68" s="7"/>
       <c r="N68" s="1"/>
-    </row>
-    <row r="69" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O68" s="1"/>
+    </row>
+    <row r="69" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A69" s="1" t="s">
         <v>45</v>
       </c>
@@ -17937,14 +17993,15 @@
       <c r="H69" s="1"/>
       <c r="I69" s="1"/>
       <c r="J69" s="1"/>
-      <c r="K69" s="7" t="s">
+      <c r="K69" s="1"/>
+      <c r="L69" s="7" t="s">
         <v>294</v>
       </c>
-      <c r="L69" s="7"/>
-      <c r="M69" s="1"/>
+      <c r="M69" s="7"/>
       <c r="N69" s="1"/>
-    </row>
-    <row r="70" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O69" s="1"/>
+    </row>
+    <row r="70" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A70" s="1" t="s">
         <v>140</v>
       </c>
@@ -17957,14 +18014,15 @@
       <c r="H70" s="1"/>
       <c r="I70" s="1"/>
       <c r="J70" s="1"/>
-      <c r="K70" s="7" t="s">
+      <c r="K70" s="1"/>
+      <c r="L70" s="7" t="s">
         <v>280</v>
       </c>
-      <c r="L70" s="7"/>
-      <c r="M70" s="1"/>
+      <c r="M70" s="7"/>
       <c r="N70" s="1"/>
-    </row>
-    <row r="71" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O70" s="1"/>
+    </row>
+    <row r="71" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A71" s="1" t="s">
         <v>138</v>
       </c>
@@ -17981,8 +18039,9 @@
       <c r="L71" s="1"/>
       <c r="M71" s="1"/>
       <c r="N71" s="1"/>
-    </row>
-    <row r="72" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O71" s="1"/>
+    </row>
+    <row r="72" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A72" s="1" t="s">
         <v>134</v>
       </c>
@@ -17999,8 +18058,9 @@
       <c r="L72" s="1"/>
       <c r="M72" s="1"/>
       <c r="N72" s="1"/>
-    </row>
-    <row r="73" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O72" s="1"/>
+    </row>
+    <row r="73" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A73" s="1" t="s">
         <v>132</v>
       </c>
@@ -18017,8 +18077,9 @@
       <c r="L73" s="1"/>
       <c r="M73" s="1"/>
       <c r="N73" s="1"/>
-    </row>
-    <row r="74" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O73" s="1"/>
+    </row>
+    <row r="74" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A74" s="1" t="s">
         <v>128</v>
       </c>
@@ -18031,12 +18092,13 @@
       <c r="H74" s="1"/>
       <c r="I74" s="1"/>
       <c r="J74" s="1"/>
-      <c r="K74" s="2"/>
+      <c r="K74" s="1"/>
       <c r="L74" s="2"/>
-      <c r="M74" s="1"/>
+      <c r="M74" s="2"/>
       <c r="N74" s="1"/>
-    </row>
-    <row r="75" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O74" s="1"/>
+    </row>
+    <row r="75" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A75" s="1" t="s">
         <v>124</v>
       </c>
@@ -18053,8 +18115,9 @@
       <c r="L75" s="1"/>
       <c r="M75" s="1"/>
       <c r="N75" s="1"/>
-    </row>
-    <row r="76" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O75" s="1"/>
+    </row>
+    <row r="76" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A76" s="1" t="s">
         <v>121</v>
       </c>
@@ -18071,8 +18134,9 @@
       <c r="L76" s="1"/>
       <c r="M76" s="1"/>
       <c r="N76" s="1"/>
-    </row>
-    <row r="77" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O76" s="1"/>
+    </row>
+    <row r="77" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A77" s="1" t="s">
         <v>119</v>
       </c>
@@ -18089,8 +18153,9 @@
       <c r="L77" s="1"/>
       <c r="M77" s="1"/>
       <c r="N77" s="1"/>
-    </row>
-    <row r="78" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O77" s="1"/>
+    </row>
+    <row r="78" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A78" s="1" t="s">
         <v>118</v>
       </c>
@@ -18107,8 +18172,9 @@
       <c r="L78" s="1"/>
       <c r="M78" s="1"/>
       <c r="N78" s="1"/>
-    </row>
-    <row r="79" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O78" s="1"/>
+    </row>
+    <row r="79" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A79" s="1" t="s">
         <v>116</v>
       </c>
@@ -18121,12 +18187,13 @@
       <c r="H79" s="1"/>
       <c r="I79" s="1"/>
       <c r="J79" s="1"/>
-      <c r="K79" s="2"/>
+      <c r="K79" s="1"/>
       <c r="L79" s="2"/>
-      <c r="M79" s="1"/>
+      <c r="M79" s="2"/>
       <c r="N79" s="1"/>
-    </row>
-    <row r="80" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O79" s="1"/>
+    </row>
+    <row r="80" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A80" s="1" t="s">
         <v>114</v>
       </c>
@@ -18143,8 +18210,9 @@
       <c r="L80" s="1"/>
       <c r="M80" s="1"/>
       <c r="N80" s="1"/>
-    </row>
-    <row r="81" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O80" s="1"/>
+    </row>
+    <row r="81" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A81" s="1" t="s">
         <v>111</v>
       </c>
@@ -18161,8 +18229,9 @@
       <c r="L81" s="1"/>
       <c r="M81" s="1"/>
       <c r="N81" s="1"/>
-    </row>
-    <row r="82" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O81" s="1"/>
+    </row>
+    <row r="82" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A82" s="1" t="s">
         <v>109</v>
       </c>
@@ -18175,12 +18244,13 @@
       <c r="H82" s="1"/>
       <c r="I82" s="1"/>
       <c r="J82" s="1"/>
-      <c r="K82" s="2"/>
+      <c r="K82" s="1"/>
       <c r="L82" s="2"/>
-      <c r="M82" s="1"/>
+      <c r="M82" s="2"/>
       <c r="N82" s="1"/>
-    </row>
-    <row r="83" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O82" s="1"/>
+    </row>
+    <row r="83" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A83" s="1" t="s">
         <v>108</v>
       </c>
@@ -18197,8 +18267,9 @@
       <c r="L83" s="1"/>
       <c r="M83" s="1"/>
       <c r="N83" s="1"/>
-    </row>
-    <row r="84" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O83" s="1"/>
+    </row>
+    <row r="84" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A84" s="1" t="s">
         <v>107</v>
       </c>
@@ -18215,8 +18286,9 @@
       <c r="L84" s="1"/>
       <c r="M84" s="1"/>
       <c r="N84" s="1"/>
-    </row>
-    <row r="85" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O84" s="1"/>
+    </row>
+    <row r="85" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A85" s="1" t="s">
         <v>105</v>
       </c>
@@ -18233,8 +18305,9 @@
       <c r="L85" s="1"/>
       <c r="M85" s="1"/>
       <c r="N85" s="1"/>
-    </row>
-    <row r="86" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O85" s="1"/>
+    </row>
+    <row r="86" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A86" s="1" t="s">
         <v>227</v>
       </c>
@@ -18251,8 +18324,9 @@
       <c r="L86" s="1"/>
       <c r="M86" s="1"/>
       <c r="N86" s="1"/>
-    </row>
-    <row r="87" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O86" s="1"/>
+    </row>
+    <row r="87" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A87" s="1" t="s">
         <v>88</v>
       </c>
@@ -18269,8 +18343,9 @@
       <c r="L87" s="1"/>
       <c r="M87" s="1"/>
       <c r="N87" s="1"/>
-    </row>
-    <row r="88" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O87" s="1"/>
+    </row>
+    <row r="88" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A88" s="1" t="s">
         <v>103</v>
       </c>
@@ -18287,8 +18362,9 @@
       <c r="L88" s="1"/>
       <c r="M88" s="1"/>
       <c r="N88" s="1"/>
-    </row>
-    <row r="89" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O88" s="1"/>
+    </row>
+    <row r="89" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A89" s="1" t="s">
         <v>101</v>
       </c>
@@ -18305,8 +18381,9 @@
       <c r="L89" s="1"/>
       <c r="M89" s="1"/>
       <c r="N89" s="1"/>
-    </row>
-    <row r="90" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O89" s="1"/>
+    </row>
+    <row r="90" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A90" s="1" t="s">
         <v>99</v>
       </c>
@@ -18323,8 +18400,9 @@
       <c r="L90" s="1"/>
       <c r="M90" s="1"/>
       <c r="N90" s="1"/>
-    </row>
-    <row r="91" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O90" s="1"/>
+    </row>
+    <row r="91" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A91" s="1" t="s">
         <v>98</v>
       </c>
@@ -18341,8 +18419,9 @@
       <c r="L91" s="1"/>
       <c r="M91" s="1"/>
       <c r="N91" s="1"/>
-    </row>
-    <row r="92" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O91" s="1"/>
+    </row>
+    <row r="92" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A92" s="1" t="s">
         <v>96</v>
       </c>
@@ -18359,8 +18438,9 @@
       <c r="L92" s="1"/>
       <c r="M92" s="1"/>
       <c r="N92" s="1"/>
-    </row>
-    <row r="93" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O92" s="1"/>
+    </row>
+    <row r="93" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A93" s="1" t="s">
         <v>94</v>
       </c>
@@ -18377,8 +18457,9 @@
       <c r="L93" s="1"/>
       <c r="M93" s="1"/>
       <c r="N93" s="1"/>
-    </row>
-    <row r="94" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O93" s="1"/>
+    </row>
+    <row r="94" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A94" s="1" t="s">
         <v>92</v>
       </c>
@@ -18395,8 +18476,9 @@
       <c r="L94" s="1"/>
       <c r="M94" s="1"/>
       <c r="N94" s="1"/>
-    </row>
-    <row r="95" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O94" s="1"/>
+    </row>
+    <row r="95" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A95" s="1" t="s">
         <v>91</v>
       </c>
@@ -18413,8 +18495,9 @@
       <c r="L95" s="1"/>
       <c r="M95" s="1"/>
       <c r="N95" s="1"/>
-    </row>
-    <row r="96" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O95" s="1"/>
+    </row>
+    <row r="96" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A96" s="1" t="s">
         <v>90</v>
       </c>
@@ -18431,8 +18514,9 @@
       <c r="L96" s="1"/>
       <c r="M96" s="1"/>
       <c r="N96" s="1"/>
-    </row>
-    <row r="97" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O96" s="1"/>
+    </row>
+    <row r="97" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A97" s="1" t="s">
         <v>229</v>
       </c>
@@ -18449,8 +18533,9 @@
       <c r="L97" s="1"/>
       <c r="M97" s="1"/>
       <c r="N97" s="1"/>
-    </row>
-    <row r="98" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O97" s="1"/>
+    </row>
+    <row r="98" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A98" s="1"/>
       <c r="B98" s="1"/>
       <c r="C98" s="1"/>
@@ -18465,8 +18550,9 @@
       <c r="L98" s="1"/>
       <c r="M98" s="1"/>
       <c r="N98" s="1"/>
-    </row>
-    <row r="99" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O98" s="1"/>
+    </row>
+    <row r="99" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A99" s="1"/>
       <c r="B99" s="1"/>
       <c r="C99" s="1"/>
@@ -18481,8 +18567,9 @@
       <c r="L99" s="1"/>
       <c r="M99" s="1"/>
       <c r="N99" s="1"/>
-    </row>
-    <row r="100" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O99" s="1"/>
+    </row>
+    <row r="100" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A100" s="1"/>
       <c r="B100" s="1"/>
       <c r="C100" s="1"/>
@@ -18497,8 +18584,9 @@
       <c r="L100" s="1"/>
       <c r="M100" s="1"/>
       <c r="N100" s="1"/>
-    </row>
-    <row r="101" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O100" s="1"/>
+    </row>
+    <row r="101" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A101" s="1"/>
       <c r="B101" s="1"/>
       <c r="C101" s="1"/>
@@ -18513,8 +18601,9 @@
       <c r="L101" s="1"/>
       <c r="M101" s="1"/>
       <c r="N101" s="1"/>
-    </row>
-    <row r="102" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O101" s="1"/>
+    </row>
+    <row r="102" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A102" s="1"/>
       <c r="B102" s="1"/>
       <c r="C102" s="1"/>
@@ -18529,8 +18618,9 @@
       <c r="L102" s="1"/>
       <c r="M102" s="1"/>
       <c r="N102" s="1"/>
-    </row>
-    <row r="103" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O102" s="1"/>
+    </row>
+    <row r="103" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A103" s="1"/>
       <c r="B103" s="1"/>
       <c r="C103" s="1"/>
@@ -18545,8 +18635,9 @@
       <c r="L103" s="1"/>
       <c r="M103" s="1"/>
       <c r="N103" s="1"/>
-    </row>
-    <row r="104" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O103" s="1"/>
+    </row>
+    <row r="104" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A104" s="1"/>
       <c r="B104" s="1"/>
       <c r="C104" s="1"/>
@@ -18561,8 +18652,9 @@
       <c r="L104" s="1"/>
       <c r="M104" s="1"/>
       <c r="N104" s="1"/>
-    </row>
-    <row r="105" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O104" s="1"/>
+    </row>
+    <row r="105" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A105" s="1"/>
       <c r="B105" s="1"/>
       <c r="C105" s="1"/>
@@ -18577,8 +18669,9 @@
       <c r="L105" s="1"/>
       <c r="M105" s="1"/>
       <c r="N105" s="1"/>
-    </row>
-    <row r="106" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O105" s="1"/>
+    </row>
+    <row r="106" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A106" s="1"/>
       <c r="B106" s="1"/>
       <c r="C106" s="1"/>
@@ -18593,8 +18686,9 @@
       <c r="L106" s="1"/>
       <c r="M106" s="1"/>
       <c r="N106" s="1"/>
-    </row>
-    <row r="107" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O106" s="1"/>
+    </row>
+    <row r="107" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A107" s="1"/>
       <c r="B107" s="1"/>
       <c r="C107" s="1"/>
@@ -18609,8 +18703,9 @@
       <c r="L107" s="1"/>
       <c r="M107" s="1"/>
       <c r="N107" s="1"/>
-    </row>
-    <row r="108" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O107" s="1"/>
+    </row>
+    <row r="108" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A108" s="1"/>
       <c r="B108" s="1"/>
       <c r="C108" s="1"/>
@@ -18625,8 +18720,9 @@
       <c r="L108" s="1"/>
       <c r="M108" s="1"/>
       <c r="N108" s="1"/>
-    </row>
-    <row r="109" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O108" s="1"/>
+    </row>
+    <row r="109" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A109" s="1"/>
       <c r="B109" s="1"/>
       <c r="C109" s="1"/>
@@ -18641,8 +18737,9 @@
       <c r="L109" s="1"/>
       <c r="M109" s="1"/>
       <c r="N109" s="1"/>
-    </row>
-    <row r="110" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O109" s="1"/>
+    </row>
+    <row r="110" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A110" s="1"/>
       <c r="B110" s="1"/>
       <c r="C110" s="1"/>
@@ -18657,8 +18754,9 @@
       <c r="L110" s="1"/>
       <c r="M110" s="1"/>
       <c r="N110" s="1"/>
-    </row>
-    <row r="111" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O110" s="1"/>
+    </row>
+    <row r="111" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A111" s="1"/>
       <c r="B111" s="1"/>
       <c r="C111" s="1"/>
@@ -18673,8 +18771,9 @@
       <c r="L111" s="1"/>
       <c r="M111" s="1"/>
       <c r="N111" s="1"/>
-    </row>
-    <row r="112" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O111" s="1"/>
+    </row>
+    <row r="112" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A112" s="1"/>
       <c r="B112" s="1"/>
       <c r="C112" s="1"/>
@@ -18689,8 +18788,9 @@
       <c r="L112" s="1"/>
       <c r="M112" s="1"/>
       <c r="N112" s="1"/>
-    </row>
-    <row r="113" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O112" s="1"/>
+    </row>
+    <row r="113" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A113" s="1"/>
       <c r="B113" s="1"/>
       <c r="C113" s="1"/>
@@ -18705,8 +18805,9 @@
       <c r="L113" s="1"/>
       <c r="M113" s="1"/>
       <c r="N113" s="1"/>
-    </row>
-    <row r="114" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O113" s="1"/>
+    </row>
+    <row r="114" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A114" s="1"/>
       <c r="B114" s="1"/>
       <c r="C114" s="1"/>
@@ -18721,8 +18822,9 @@
       <c r="L114" s="1"/>
       <c r="M114" s="1"/>
       <c r="N114" s="1"/>
-    </row>
-    <row r="115" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O114" s="1"/>
+    </row>
+    <row r="115" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A115" s="1"/>
       <c r="B115" s="1"/>
       <c r="C115" s="1"/>
@@ -18737,8 +18839,9 @@
       <c r="L115" s="1"/>
       <c r="M115" s="1"/>
       <c r="N115" s="1"/>
-    </row>
-    <row r="116" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O115" s="1"/>
+    </row>
+    <row r="116" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A116" s="1"/>
       <c r="B116" s="1"/>
       <c r="C116" s="1"/>
@@ -18753,8 +18856,9 @@
       <c r="L116" s="1"/>
       <c r="M116" s="1"/>
       <c r="N116" s="1"/>
-    </row>
-    <row r="117" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O116" s="1"/>
+    </row>
+    <row r="117" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A117" s="1"/>
       <c r="B117" s="1"/>
       <c r="C117" s="1"/>
@@ -18769,8 +18873,9 @@
       <c r="L117" s="1"/>
       <c r="M117" s="1"/>
       <c r="N117" s="1"/>
-    </row>
-    <row r="118" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O117" s="1"/>
+    </row>
+    <row r="118" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A118" s="1"/>
       <c r="B118" s="1"/>
       <c r="C118" s="1"/>
@@ -18785,8 +18890,9 @@
       <c r="L118" s="1"/>
       <c r="M118" s="1"/>
       <c r="N118" s="1"/>
-    </row>
-    <row r="119" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O118" s="1"/>
+    </row>
+    <row r="119" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A119" s="1"/>
       <c r="B119" s="1"/>
       <c r="C119" s="1"/>
@@ -18801,8 +18907,9 @@
       <c r="L119" s="1"/>
       <c r="M119" s="1"/>
       <c r="N119" s="1"/>
-    </row>
-    <row r="120" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O119" s="1"/>
+    </row>
+    <row r="120" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A120" s="1"/>
       <c r="B120" s="1"/>
       <c r="C120" s="1"/>
@@ -18817,8 +18924,9 @@
       <c r="L120" s="1"/>
       <c r="M120" s="1"/>
       <c r="N120" s="1"/>
-    </row>
-    <row r="121" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O120" s="1"/>
+    </row>
+    <row r="121" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A121" s="1"/>
       <c r="B121" s="1"/>
       <c r="C121" s="1"/>
@@ -18833,8 +18941,9 @@
       <c r="L121" s="1"/>
       <c r="M121" s="1"/>
       <c r="N121" s="1"/>
-    </row>
-    <row r="122" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O121" s="1"/>
+    </row>
+    <row r="122" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A122" s="1"/>
       <c r="B122" s="1"/>
       <c r="C122" s="1"/>
@@ -18849,8 +18958,9 @@
       <c r="L122" s="1"/>
       <c r="M122" s="1"/>
       <c r="N122" s="1"/>
-    </row>
-    <row r="123" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O122" s="1"/>
+    </row>
+    <row r="123" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A123" s="1"/>
       <c r="B123" s="1"/>
       <c r="C123" s="1"/>
@@ -18865,8 +18975,9 @@
       <c r="L123" s="1"/>
       <c r="M123" s="1"/>
       <c r="N123" s="1"/>
-    </row>
-    <row r="124" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O123" s="1"/>
+    </row>
+    <row r="124" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A124" s="1"/>
       <c r="B124" s="1"/>
       <c r="C124" s="1"/>
@@ -18881,8 +18992,9 @@
       <c r="L124" s="1"/>
       <c r="M124" s="1"/>
       <c r="N124" s="1"/>
-    </row>
-    <row r="125" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O124" s="1"/>
+    </row>
+    <row r="125" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A125" s="1"/>
       <c r="B125" s="1"/>
       <c r="C125" s="1"/>
@@ -18897,8 +19009,9 @@
       <c r="L125" s="1"/>
       <c r="M125" s="1"/>
       <c r="N125" s="1"/>
-    </row>
-    <row r="126" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O125" s="1"/>
+    </row>
+    <row r="126" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A126" s="1"/>
       <c r="B126" s="1"/>
       <c r="C126" s="1"/>
@@ -18913,8 +19026,9 @@
       <c r="L126" s="1"/>
       <c r="M126" s="1"/>
       <c r="N126" s="1"/>
-    </row>
-    <row r="127" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O126" s="1"/>
+    </row>
+    <row r="127" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A127" s="1"/>
       <c r="B127" s="1"/>
       <c r="C127" s="1"/>
@@ -18929,8 +19043,9 @@
       <c r="L127" s="1"/>
       <c r="M127" s="1"/>
       <c r="N127" s="1"/>
-    </row>
-    <row r="128" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O127" s="1"/>
+    </row>
+    <row r="128" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A128" s="1"/>
       <c r="B128" s="1"/>
       <c r="C128" s="1"/>
@@ -18945,8 +19060,9 @@
       <c r="L128" s="1"/>
       <c r="M128" s="1"/>
       <c r="N128" s="1"/>
-    </row>
-    <row r="129" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O128" s="1"/>
+    </row>
+    <row r="129" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A129" s="1"/>
       <c r="B129" s="1"/>
       <c r="C129" s="1"/>
@@ -18961,8 +19077,9 @@
       <c r="L129" s="1"/>
       <c r="M129" s="1"/>
       <c r="N129" s="1"/>
-    </row>
-    <row r="130" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O129" s="1"/>
+    </row>
+    <row r="130" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A130" s="1"/>
       <c r="B130" s="1"/>
       <c r="C130" s="1"/>
@@ -18977,8 +19094,9 @@
       <c r="L130" s="1"/>
       <c r="M130" s="1"/>
       <c r="N130" s="1"/>
-    </row>
-    <row r="131" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O130" s="1"/>
+    </row>
+    <row r="131" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A131" s="1"/>
       <c r="B131" s="1"/>
       <c r="C131" s="1"/>
@@ -18993,8 +19111,9 @@
       <c r="L131" s="1"/>
       <c r="M131" s="1"/>
       <c r="N131" s="1"/>
-    </row>
-    <row r="132" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O131" s="1"/>
+    </row>
+    <row r="132" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A132" s="1"/>
       <c r="B132" s="1"/>
       <c r="C132" s="1"/>
@@ -19009,8 +19128,9 @@
       <c r="L132" s="1"/>
       <c r="M132" s="1"/>
       <c r="N132" s="1"/>
-    </row>
-    <row r="133" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O132" s="1"/>
+    </row>
+    <row r="133" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A133" s="1"/>
       <c r="B133" s="1"/>
       <c r="C133" s="1"/>
@@ -19025,8 +19145,9 @@
       <c r="L133" s="1"/>
       <c r="M133" s="1"/>
       <c r="N133" s="1"/>
-    </row>
-    <row r="134" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O133" s="1"/>
+    </row>
+    <row r="134" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A134" s="1"/>
       <c r="B134" s="1"/>
       <c r="C134" s="1"/>
@@ -19041,8 +19162,9 @@
       <c r="L134" s="1"/>
       <c r="M134" s="1"/>
       <c r="N134" s="1"/>
-    </row>
-    <row r="135" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O134" s="1"/>
+    </row>
+    <row r="135" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A135" s="1"/>
       <c r="B135" s="1"/>
       <c r="C135" s="1"/>
@@ -19057,8 +19179,9 @@
       <c r="L135" s="1"/>
       <c r="M135" s="1"/>
       <c r="N135" s="1"/>
-    </row>
-    <row r="136" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O135" s="1"/>
+    </row>
+    <row r="136" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A136" s="1"/>
       <c r="B136" s="1"/>
       <c r="C136" s="1"/>
@@ -19073,8 +19196,9 @@
       <c r="L136" s="1"/>
       <c r="M136" s="1"/>
       <c r="N136" s="1"/>
-    </row>
-    <row r="137" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O136" s="1"/>
+    </row>
+    <row r="137" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A137" s="1"/>
       <c r="B137" s="1"/>
       <c r="C137" s="1"/>
@@ -19089,8 +19213,9 @@
       <c r="L137" s="1"/>
       <c r="M137" s="1"/>
       <c r="N137" s="1"/>
-    </row>
-    <row r="138" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O137" s="1"/>
+    </row>
+    <row r="138" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A138" s="1"/>
       <c r="B138" s="1"/>
       <c r="C138" s="1"/>
@@ -19105,8 +19230,9 @@
       <c r="L138" s="1"/>
       <c r="M138" s="1"/>
       <c r="N138" s="1"/>
-    </row>
-    <row r="139" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O138" s="1"/>
+    </row>
+    <row r="139" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A139" s="1"/>
       <c r="B139" s="1"/>
       <c r="C139" s="1"/>
@@ -19121,8 +19247,9 @@
       <c r="L139" s="1"/>
       <c r="M139" s="1"/>
       <c r="N139" s="1"/>
-    </row>
-    <row r="140" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O139" s="1"/>
+    </row>
+    <row r="140" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A140" s="1"/>
       <c r="B140" s="1"/>
       <c r="C140" s="1"/>
@@ -19137,8 +19264,9 @@
       <c r="L140" s="1"/>
       <c r="M140" s="1"/>
       <c r="N140" s="1"/>
-    </row>
-    <row r="141" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O140" s="1"/>
+    </row>
+    <row r="141" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A141" s="1"/>
       <c r="B141" s="1"/>
       <c r="C141" s="1"/>
@@ -19153,8 +19281,9 @@
       <c r="L141" s="1"/>
       <c r="M141" s="1"/>
       <c r="N141" s="1"/>
-    </row>
-    <row r="142" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O141" s="1"/>
+    </row>
+    <row r="142" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A142" s="1"/>
       <c r="B142" s="1"/>
       <c r="C142" s="1"/>
@@ -19169,8 +19298,9 @@
       <c r="L142" s="1"/>
       <c r="M142" s="1"/>
       <c r="N142" s="1"/>
-    </row>
-    <row r="143" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O142" s="1"/>
+    </row>
+    <row r="143" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A143" s="1"/>
       <c r="B143" s="1"/>
       <c r="C143" s="1"/>
@@ -19185,8 +19315,9 @@
       <c r="L143" s="1"/>
       <c r="M143" s="1"/>
       <c r="N143" s="1"/>
-    </row>
-    <row r="144" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O143" s="1"/>
+    </row>
+    <row r="144" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A144" s="1"/>
       <c r="B144" s="1"/>
       <c r="C144" s="1"/>
@@ -19201,8 +19332,9 @@
       <c r="L144" s="1"/>
       <c r="M144" s="1"/>
       <c r="N144" s="1"/>
-    </row>
-    <row r="145" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O144" s="1"/>
+    </row>
+    <row r="145" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A145" s="1"/>
       <c r="B145" s="1"/>
       <c r="C145" s="1"/>
@@ -19217,8 +19349,9 @@
       <c r="L145" s="1"/>
       <c r="M145" s="1"/>
       <c r="N145" s="1"/>
-    </row>
-    <row r="146" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O145" s="1"/>
+    </row>
+    <row r="146" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A146" s="1"/>
       <c r="B146" s="1"/>
       <c r="C146" s="1"/>
@@ -19233,8 +19366,9 @@
       <c r="L146" s="1"/>
       <c r="M146" s="1"/>
       <c r="N146" s="1"/>
-    </row>
-    <row r="147" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O146" s="1"/>
+    </row>
+    <row r="147" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A147" s="1"/>
       <c r="B147" s="1"/>
       <c r="C147" s="1"/>
@@ -19249,8 +19383,9 @@
       <c r="L147" s="1"/>
       <c r="M147" s="1"/>
       <c r="N147" s="1"/>
-    </row>
-    <row r="148" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O147" s="1"/>
+    </row>
+    <row r="148" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A148" s="1"/>
       <c r="B148" s="1"/>
       <c r="C148" s="1"/>
@@ -19265,8 +19400,9 @@
       <c r="L148" s="1"/>
       <c r="M148" s="1"/>
       <c r="N148" s="1"/>
-    </row>
-    <row r="149" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O148" s="1"/>
+    </row>
+    <row r="149" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A149" s="1"/>
       <c r="B149" s="1"/>
       <c r="C149" s="1"/>
@@ -19281,8 +19417,9 @@
       <c r="L149" s="1"/>
       <c r="M149" s="1"/>
       <c r="N149" s="1"/>
-    </row>
-    <row r="150" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O149" s="1"/>
+    </row>
+    <row r="150" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A150" s="1"/>
       <c r="B150" s="1"/>
       <c r="C150" s="1"/>
@@ -19297,8 +19434,9 @@
       <c r="L150" s="1"/>
       <c r="M150" s="1"/>
       <c r="N150" s="1"/>
-    </row>
-    <row r="151" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O150" s="1"/>
+    </row>
+    <row r="151" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A151" s="1"/>
       <c r="B151" s="1"/>
       <c r="C151" s="1"/>
@@ -19313,8 +19451,9 @@
       <c r="L151" s="1"/>
       <c r="M151" s="1"/>
       <c r="N151" s="1"/>
-    </row>
-    <row r="152" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O151" s="1"/>
+    </row>
+    <row r="152" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A152" s="1"/>
       <c r="B152" s="1"/>
       <c r="C152" s="1"/>
@@ -19329,8 +19468,9 @@
       <c r="L152" s="1"/>
       <c r="M152" s="1"/>
       <c r="N152" s="1"/>
-    </row>
-    <row r="153" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O152" s="1"/>
+    </row>
+    <row r="153" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A153" s="1"/>
       <c r="B153" s="1"/>
       <c r="C153" s="1"/>
@@ -19345,8 +19485,9 @@
       <c r="L153" s="1"/>
       <c r="M153" s="1"/>
       <c r="N153" s="1"/>
-    </row>
-    <row r="154" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O153" s="1"/>
+    </row>
+    <row r="154" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A154" s="1"/>
       <c r="B154" s="1"/>
       <c r="C154" s="1"/>
@@ -19361,8 +19502,9 @@
       <c r="L154" s="1"/>
       <c r="M154" s="1"/>
       <c r="N154" s="1"/>
-    </row>
-    <row r="155" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O154" s="1"/>
+    </row>
+    <row r="155" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A155" s="1"/>
       <c r="B155" s="1"/>
       <c r="C155" s="1"/>
@@ -19377,8 +19519,9 @@
       <c r="L155" s="1"/>
       <c r="M155" s="1"/>
       <c r="N155" s="1"/>
-    </row>
-    <row r="156" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O155" s="1"/>
+    </row>
+    <row r="156" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A156" s="1"/>
       <c r="B156" s="1"/>
       <c r="C156" s="1"/>
@@ -19393,8 +19536,9 @@
       <c r="L156" s="1"/>
       <c r="M156" s="1"/>
       <c r="N156" s="1"/>
-    </row>
-    <row r="157" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O156" s="1"/>
+    </row>
+    <row r="157" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A157" s="1"/>
       <c r="B157" s="1"/>
       <c r="C157" s="1"/>
@@ -19409,8 +19553,9 @@
       <c r="L157" s="1"/>
       <c r="M157" s="1"/>
       <c r="N157" s="1"/>
-    </row>
-    <row r="158" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O157" s="1"/>
+    </row>
+    <row r="158" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A158" s="1"/>
       <c r="B158" s="1"/>
       <c r="C158" s="1"/>
@@ -19425,8 +19570,9 @@
       <c r="L158" s="1"/>
       <c r="M158" s="1"/>
       <c r="N158" s="1"/>
-    </row>
-    <row r="159" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O158" s="1"/>
+    </row>
+    <row r="159" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A159" s="1"/>
       <c r="B159" s="1"/>
       <c r="C159" s="1"/>
@@ -19441,8 +19587,9 @@
       <c r="L159" s="1"/>
       <c r="M159" s="1"/>
       <c r="N159" s="1"/>
-    </row>
-    <row r="160" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O159" s="1"/>
+    </row>
+    <row r="160" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A160" s="1"/>
       <c r="B160" s="1"/>
       <c r="C160" s="1"/>
@@ -19457,8 +19604,9 @@
       <c r="L160" s="1"/>
       <c r="M160" s="1"/>
       <c r="N160" s="1"/>
-    </row>
-    <row r="161" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O160" s="1"/>
+    </row>
+    <row r="161" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A161" s="1"/>
       <c r="B161" s="1"/>
       <c r="C161" s="1"/>
@@ -19473,8 +19621,9 @@
       <c r="L161" s="1"/>
       <c r="M161" s="1"/>
       <c r="N161" s="1"/>
-    </row>
-    <row r="162" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O161" s="1"/>
+    </row>
+    <row r="162" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A162" s="1"/>
       <c r="B162" s="1"/>
       <c r="C162" s="1"/>
@@ -19489,8 +19638,9 @@
       <c r="L162" s="1"/>
       <c r="M162" s="1"/>
       <c r="N162" s="1"/>
-    </row>
-    <row r="163" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O162" s="1"/>
+    </row>
+    <row r="163" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A163" s="1"/>
       <c r="B163" s="1"/>
       <c r="C163" s="1"/>
@@ -19505,8 +19655,9 @@
       <c r="L163" s="1"/>
       <c r="M163" s="1"/>
       <c r="N163" s="1"/>
-    </row>
-    <row r="164" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O163" s="1"/>
+    </row>
+    <row r="164" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A164" s="1"/>
       <c r="B164" s="1"/>
       <c r="C164" s="1"/>
@@ -19521,8 +19672,9 @@
       <c r="L164" s="1"/>
       <c r="M164" s="1"/>
       <c r="N164" s="1"/>
-    </row>
-    <row r="165" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O164" s="1"/>
+    </row>
+    <row r="165" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A165" s="1"/>
       <c r="B165" s="1"/>
       <c r="C165" s="1"/>
@@ -19537,8 +19689,9 @@
       <c r="L165" s="1"/>
       <c r="M165" s="1"/>
       <c r="N165" s="1"/>
-    </row>
-    <row r="166" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O165" s="1"/>
+    </row>
+    <row r="166" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A166" s="1"/>
       <c r="B166" s="1"/>
       <c r="C166" s="1"/>
@@ -19553,8 +19706,9 @@
       <c r="L166" s="1"/>
       <c r="M166" s="1"/>
       <c r="N166" s="1"/>
-    </row>
-    <row r="167" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O166" s="1"/>
+    </row>
+    <row r="167" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A167" s="1"/>
       <c r="B167" s="1"/>
       <c r="C167" s="1"/>
@@ -19569,8 +19723,9 @@
       <c r="L167" s="1"/>
       <c r="M167" s="1"/>
       <c r="N167" s="1"/>
-    </row>
-    <row r="168" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O167" s="1"/>
+    </row>
+    <row r="168" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A168" s="1"/>
       <c r="B168" s="1"/>
       <c r="C168" s="1"/>
@@ -19585,8 +19740,9 @@
       <c r="L168" s="1"/>
       <c r="M168" s="1"/>
       <c r="N168" s="1"/>
-    </row>
-    <row r="169" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O168" s="1"/>
+    </row>
+    <row r="169" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A169" s="1"/>
       <c r="B169" s="1"/>
       <c r="C169" s="1"/>
@@ -19601,8 +19757,9 @@
       <c r="L169" s="1"/>
       <c r="M169" s="1"/>
       <c r="N169" s="1"/>
-    </row>
-    <row r="170" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O169" s="1"/>
+    </row>
+    <row r="170" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A170" s="1"/>
       <c r="B170" s="1"/>
       <c r="C170" s="1"/>
@@ -19617,8 +19774,9 @@
       <c r="L170" s="1"/>
       <c r="M170" s="1"/>
       <c r="N170" s="1"/>
-    </row>
-    <row r="171" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O170" s="1"/>
+    </row>
+    <row r="171" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A171" s="1"/>
       <c r="B171" s="1"/>
       <c r="C171" s="1"/>
@@ -19633,8 +19791,9 @@
       <c r="L171" s="1"/>
       <c r="M171" s="1"/>
       <c r="N171" s="1"/>
-    </row>
-    <row r="172" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O171" s="1"/>
+    </row>
+    <row r="172" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A172" s="1"/>
       <c r="B172" s="1"/>
       <c r="C172" s="1"/>
@@ -19649,8 +19808,9 @@
       <c r="L172" s="1"/>
       <c r="M172" s="1"/>
       <c r="N172" s="1"/>
-    </row>
-    <row r="173" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O172" s="1"/>
+    </row>
+    <row r="173" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A173" s="1"/>
       <c r="B173" s="1"/>
       <c r="C173" s="1"/>
@@ -19665,8 +19825,9 @@
       <c r="L173" s="1"/>
       <c r="M173" s="1"/>
       <c r="N173" s="1"/>
-    </row>
-    <row r="174" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O173" s="1"/>
+    </row>
+    <row r="174" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A174" s="1"/>
       <c r="B174" s="1"/>
       <c r="C174" s="1"/>
@@ -19681,8 +19842,9 @@
       <c r="L174" s="1"/>
       <c r="M174" s="1"/>
       <c r="N174" s="1"/>
-    </row>
-    <row r="175" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O174" s="1"/>
+    </row>
+    <row r="175" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A175" s="1"/>
       <c r="B175" s="1"/>
       <c r="C175" s="1"/>
@@ -19697,8 +19859,9 @@
       <c r="L175" s="1"/>
       <c r="M175" s="1"/>
       <c r="N175" s="1"/>
-    </row>
-    <row r="176" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O175" s="1"/>
+    </row>
+    <row r="176" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A176" s="1"/>
       <c r="B176" s="1"/>
       <c r="C176" s="1"/>
@@ -19713,8 +19876,9 @@
       <c r="L176" s="1"/>
       <c r="M176" s="1"/>
       <c r="N176" s="1"/>
-    </row>
-    <row r="177" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O176" s="1"/>
+    </row>
+    <row r="177" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A177" s="1"/>
       <c r="B177" s="1"/>
       <c r="C177" s="1"/>
@@ -19729,8 +19893,9 @@
       <c r="L177" s="1"/>
       <c r="M177" s="1"/>
       <c r="N177" s="1"/>
-    </row>
-    <row r="178" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O177" s="1"/>
+    </row>
+    <row r="178" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A178" s="1"/>
       <c r="B178" s="1"/>
       <c r="C178" s="1"/>
@@ -19745,8 +19910,9 @@
       <c r="L178" s="1"/>
       <c r="M178" s="1"/>
       <c r="N178" s="1"/>
-    </row>
-    <row r="179" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O178" s="1"/>
+    </row>
+    <row r="179" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A179" s="1"/>
       <c r="B179" s="1"/>
       <c r="C179" s="1"/>
@@ -19761,8 +19927,9 @@
       <c r="L179" s="1"/>
       <c r="M179" s="1"/>
       <c r="N179" s="1"/>
-    </row>
-    <row r="180" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O179" s="1"/>
+    </row>
+    <row r="180" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A180" s="1"/>
       <c r="B180" s="1"/>
       <c r="C180" s="1"/>
@@ -19777,8 +19944,9 @@
       <c r="L180" s="1"/>
       <c r="M180" s="1"/>
       <c r="N180" s="1"/>
-    </row>
-    <row r="181" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O180" s="1"/>
+    </row>
+    <row r="181" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A181" s="1"/>
       <c r="B181" s="1"/>
       <c r="C181" s="1"/>
@@ -19793,8 +19961,9 @@
       <c r="L181" s="1"/>
       <c r="M181" s="1"/>
       <c r="N181" s="1"/>
-    </row>
-    <row r="182" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O181" s="1"/>
+    </row>
+    <row r="182" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A182" s="1"/>
       <c r="B182" s="1"/>
       <c r="C182" s="1"/>
@@ -19809,8 +19978,9 @@
       <c r="L182" s="1"/>
       <c r="M182" s="1"/>
       <c r="N182" s="1"/>
-    </row>
-    <row r="183" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O182" s="1"/>
+    </row>
+    <row r="183" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A183" s="1"/>
       <c r="B183" s="1"/>
       <c r="C183" s="1"/>
@@ -19825,8 +19995,9 @@
       <c r="L183" s="1"/>
       <c r="M183" s="1"/>
       <c r="N183" s="1"/>
-    </row>
-    <row r="184" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O183" s="1"/>
+    </row>
+    <row r="184" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A184" s="1"/>
       <c r="B184" s="1"/>
       <c r="C184" s="1"/>
@@ -19841,8 +20012,9 @@
       <c r="L184" s="1"/>
       <c r="M184" s="1"/>
       <c r="N184" s="1"/>
-    </row>
-    <row r="185" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O184" s="1"/>
+    </row>
+    <row r="185" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A185" s="1"/>
       <c r="B185" s="1"/>
       <c r="C185" s="1"/>
@@ -19857,8 +20029,9 @@
       <c r="L185" s="1"/>
       <c r="M185" s="1"/>
       <c r="N185" s="1"/>
-    </row>
-    <row r="186" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O185" s="1"/>
+    </row>
+    <row r="186" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A186" s="1"/>
       <c r="B186" s="1"/>
       <c r="C186" s="1"/>
@@ -19873,8 +20046,9 @@
       <c r="L186" s="1"/>
       <c r="M186" s="1"/>
       <c r="N186" s="1"/>
-    </row>
-    <row r="187" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O186" s="1"/>
+    </row>
+    <row r="187" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A187" s="1"/>
       <c r="B187" s="1"/>
       <c r="C187" s="1"/>
@@ -19889,8 +20063,9 @@
       <c r="L187" s="1"/>
       <c r="M187" s="1"/>
       <c r="N187" s="1"/>
-    </row>
-    <row r="188" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O187" s="1"/>
+    </row>
+    <row r="188" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A188" s="1"/>
       <c r="B188" s="1"/>
       <c r="C188" s="1"/>
@@ -19905,8 +20080,9 @@
       <c r="L188" s="1"/>
       <c r="M188" s="1"/>
       <c r="N188" s="1"/>
-    </row>
-    <row r="189" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O188" s="1"/>
+    </row>
+    <row r="189" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A189" s="1"/>
       <c r="B189" s="1"/>
       <c r="C189" s="1"/>
@@ -19921,8 +20097,9 @@
       <c r="L189" s="1"/>
       <c r="M189" s="1"/>
       <c r="N189" s="1"/>
-    </row>
-    <row r="190" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O189" s="1"/>
+    </row>
+    <row r="190" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A190" s="1"/>
       <c r="B190" s="1"/>
       <c r="C190" s="1"/>
@@ -19937,8 +20114,9 @@
       <c r="L190" s="1"/>
       <c r="M190" s="1"/>
       <c r="N190" s="1"/>
-    </row>
-    <row r="191" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O190" s="1"/>
+    </row>
+    <row r="191" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A191" s="1"/>
       <c r="B191" s="1"/>
       <c r="C191" s="1"/>
@@ -19953,8 +20131,9 @@
       <c r="L191" s="1"/>
       <c r="M191" s="1"/>
       <c r="N191" s="1"/>
-    </row>
-    <row r="192" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O191" s="1"/>
+    </row>
+    <row r="192" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A192" s="1"/>
       <c r="B192" s="1"/>
       <c r="C192" s="1"/>
@@ -19969,8 +20148,9 @@
       <c r="L192" s="1"/>
       <c r="M192" s="1"/>
       <c r="N192" s="1"/>
-    </row>
-    <row r="193" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O192" s="1"/>
+    </row>
+    <row r="193" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A193" s="1"/>
       <c r="B193" s="1"/>
       <c r="C193" s="1"/>
@@ -19985,8 +20165,9 @@
       <c r="L193" s="1"/>
       <c r="M193" s="1"/>
       <c r="N193" s="1"/>
-    </row>
-    <row r="194" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O193" s="1"/>
+    </row>
+    <row r="194" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A194" s="1"/>
       <c r="B194" s="1"/>
       <c r="C194" s="1"/>
@@ -20001,8 +20182,9 @@
       <c r="L194" s="1"/>
       <c r="M194" s="1"/>
       <c r="N194" s="1"/>
-    </row>
-    <row r="195" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O194" s="1"/>
+    </row>
+    <row r="195" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A195" s="1"/>
       <c r="B195" s="1"/>
       <c r="C195" s="1"/>
@@ -20017,8 +20199,9 @@
       <c r="L195" s="1"/>
       <c r="M195" s="1"/>
       <c r="N195" s="1"/>
-    </row>
-    <row r="196" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O195" s="1"/>
+    </row>
+    <row r="196" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A196" s="1"/>
       <c r="B196" s="1"/>
       <c r="C196" s="1"/>
@@ -20033,8 +20216,9 @@
       <c r="L196" s="1"/>
       <c r="M196" s="1"/>
       <c r="N196" s="1"/>
-    </row>
-    <row r="197" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O196" s="1"/>
+    </row>
+    <row r="197" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A197" s="1"/>
       <c r="B197" s="1"/>
       <c r="C197" s="1"/>
@@ -20049,8 +20233,9 @@
       <c r="L197" s="1"/>
       <c r="M197" s="1"/>
       <c r="N197" s="1"/>
-    </row>
-    <row r="198" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O197" s="1"/>
+    </row>
+    <row r="198" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A198" s="1"/>
       <c r="B198" s="1"/>
       <c r="C198" s="1"/>
@@ -20065,8 +20250,9 @@
       <c r="L198" s="1"/>
       <c r="M198" s="1"/>
       <c r="N198" s="1"/>
-    </row>
-    <row r="199" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O198" s="1"/>
+    </row>
+    <row r="199" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A199" s="1"/>
       <c r="B199" s="1"/>
       <c r="C199" s="1"/>
@@ -20081,8 +20267,9 @@
       <c r="L199" s="1"/>
       <c r="M199" s="1"/>
       <c r="N199" s="1"/>
-    </row>
-    <row r="200" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O199" s="1"/>
+    </row>
+    <row r="200" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A200" s="1"/>
       <c r="B200" s="1"/>
       <c r="C200" s="1"/>
@@ -20097,8 +20284,9 @@
       <c r="L200" s="1"/>
       <c r="M200" s="1"/>
       <c r="N200" s="1"/>
-    </row>
-    <row r="201" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O200" s="1"/>
+    </row>
+    <row r="201" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A201" s="1"/>
       <c r="B201" s="1"/>
       <c r="C201" s="1"/>
@@ -20113,8 +20301,9 @@
       <c r="L201" s="1"/>
       <c r="M201" s="1"/>
       <c r="N201" s="1"/>
-    </row>
-    <row r="202" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O201" s="1"/>
+    </row>
+    <row r="202" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A202" s="1"/>
       <c r="B202" s="1"/>
       <c r="C202" s="1"/>
@@ -20129,8 +20318,9 @@
       <c r="L202" s="1"/>
       <c r="M202" s="1"/>
       <c r="N202" s="1"/>
-    </row>
-    <row r="203" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O202" s="1"/>
+    </row>
+    <row r="203" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A203" s="1"/>
       <c r="B203" s="1"/>
       <c r="C203" s="1"/>
@@ -20145,8 +20335,9 @@
       <c r="L203" s="1"/>
       <c r="M203" s="1"/>
       <c r="N203" s="1"/>
-    </row>
-    <row r="204" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O203" s="1"/>
+    </row>
+    <row r="204" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A204" s="1"/>
       <c r="B204" s="1"/>
       <c r="C204" s="1"/>
@@ -20161,8 +20352,9 @@
       <c r="L204" s="1"/>
       <c r="M204" s="1"/>
       <c r="N204" s="1"/>
-    </row>
-    <row r="205" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O204" s="1"/>
+    </row>
+    <row r="205" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A205" s="1"/>
       <c r="B205" s="1"/>
       <c r="C205" s="1"/>
@@ -20177,8 +20369,9 @@
       <c r="L205" s="1"/>
       <c r="M205" s="1"/>
       <c r="N205" s="1"/>
-    </row>
-    <row r="206" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O205" s="1"/>
+    </row>
+    <row r="206" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A206" s="1"/>
       <c r="B206" s="1"/>
       <c r="C206" s="1"/>
@@ -20193,8 +20386,9 @@
       <c r="L206" s="1"/>
       <c r="M206" s="1"/>
       <c r="N206" s="1"/>
-    </row>
-    <row r="207" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O206" s="1"/>
+    </row>
+    <row r="207" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A207" s="1"/>
       <c r="B207" s="1"/>
       <c r="C207" s="1"/>
@@ -20209,8 +20403,9 @@
       <c r="L207" s="1"/>
       <c r="M207" s="1"/>
       <c r="N207" s="1"/>
-    </row>
-    <row r="208" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O207" s="1"/>
+    </row>
+    <row r="208" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A208" s="1"/>
       <c r="B208" s="1"/>
       <c r="C208" s="1"/>
@@ -20225,8 +20420,9 @@
       <c r="L208" s="1"/>
       <c r="M208" s="1"/>
       <c r="N208" s="1"/>
-    </row>
-    <row r="209" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O208" s="1"/>
+    </row>
+    <row r="209" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A209" s="1"/>
       <c r="B209" s="1"/>
       <c r="C209" s="1"/>
@@ -20241,8 +20437,9 @@
       <c r="L209" s="1"/>
       <c r="M209" s="1"/>
       <c r="N209" s="1"/>
-    </row>
-    <row r="210" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O209" s="1"/>
+    </row>
+    <row r="210" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A210" s="1"/>
       <c r="B210" s="1"/>
       <c r="C210" s="1"/>
@@ -20257,8 +20454,9 @@
       <c r="L210" s="1"/>
       <c r="M210" s="1"/>
       <c r="N210" s="1"/>
-    </row>
-    <row r="211" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O210" s="1"/>
+    </row>
+    <row r="211" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A211" s="1"/>
       <c r="B211" s="1"/>
       <c r="C211" s="1"/>
@@ -20273,8 +20471,9 @@
       <c r="L211" s="1"/>
       <c r="M211" s="1"/>
       <c r="N211" s="1"/>
-    </row>
-    <row r="212" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O211" s="1"/>
+    </row>
+    <row r="212" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A212" s="1"/>
       <c r="B212" s="1"/>
       <c r="C212" s="1"/>
@@ -20289,8 +20488,9 @@
       <c r="L212" s="1"/>
       <c r="M212" s="1"/>
       <c r="N212" s="1"/>
-    </row>
-    <row r="213" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O212" s="1"/>
+    </row>
+    <row r="213" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A213" s="1"/>
       <c r="B213" s="1"/>
       <c r="C213" s="1"/>
@@ -20305,8 +20505,9 @@
       <c r="L213" s="1"/>
       <c r="M213" s="1"/>
       <c r="N213" s="1"/>
-    </row>
-    <row r="214" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O213" s="1"/>
+    </row>
+    <row r="214" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A214" s="1"/>
       <c r="B214" s="1"/>
       <c r="C214" s="1"/>
@@ -20321,8 +20522,9 @@
       <c r="L214" s="1"/>
       <c r="M214" s="1"/>
       <c r="N214" s="1"/>
-    </row>
-    <row r="215" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O214" s="1"/>
+    </row>
+    <row r="215" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A215" s="1"/>
       <c r="B215" s="1"/>
       <c r="C215" s="1"/>
@@ -20337,8 +20539,9 @@
       <c r="L215" s="1"/>
       <c r="M215" s="1"/>
       <c r="N215" s="1"/>
-    </row>
-    <row r="216" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O215" s="1"/>
+    </row>
+    <row r="216" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A216" s="1"/>
       <c r="B216" s="1"/>
       <c r="C216" s="1"/>
@@ -20353,8 +20556,9 @@
       <c r="L216" s="1"/>
       <c r="M216" s="1"/>
       <c r="N216" s="1"/>
-    </row>
-    <row r="217" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O216" s="1"/>
+    </row>
+    <row r="217" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A217" s="1"/>
       <c r="B217" s="1"/>
       <c r="C217" s="1"/>
@@ -20369,8 +20573,9 @@
       <c r="L217" s="1"/>
       <c r="M217" s="1"/>
       <c r="N217" s="1"/>
-    </row>
-    <row r="218" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O217" s="1"/>
+    </row>
+    <row r="218" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A218" s="1"/>
       <c r="B218" s="1"/>
       <c r="C218" s="1"/>
@@ -20385,8 +20590,9 @@
       <c r="L218" s="1"/>
       <c r="M218" s="1"/>
       <c r="N218" s="1"/>
-    </row>
-    <row r="219" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O218" s="1"/>
+    </row>
+    <row r="219" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A219" s="1"/>
       <c r="B219" s="1"/>
       <c r="C219" s="1"/>
@@ -20401,8 +20607,9 @@
       <c r="L219" s="1"/>
       <c r="M219" s="1"/>
       <c r="N219" s="1"/>
-    </row>
-    <row r="220" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O219" s="1"/>
+    </row>
+    <row r="220" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A220" s="1"/>
       <c r="B220" s="1"/>
       <c r="C220" s="1"/>
@@ -20417,8 +20624,9 @@
       <c r="L220" s="1"/>
       <c r="M220" s="1"/>
       <c r="N220" s="1"/>
-    </row>
-    <row r="221" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O220" s="1"/>
+    </row>
+    <row r="221" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A221" s="1"/>
       <c r="B221" s="1"/>
       <c r="C221" s="1"/>
@@ -20433,8 +20641,9 @@
       <c r="L221" s="1"/>
       <c r="M221" s="1"/>
       <c r="N221" s="1"/>
-    </row>
-    <row r="222" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O221" s="1"/>
+    </row>
+    <row r="222" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A222" s="1"/>
       <c r="B222" s="1"/>
       <c r="C222" s="1"/>
@@ -20449,8 +20658,9 @@
       <c r="L222" s="1"/>
       <c r="M222" s="1"/>
       <c r="N222" s="1"/>
-    </row>
-    <row r="223" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O222" s="1"/>
+    </row>
+    <row r="223" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A223" s="1"/>
       <c r="B223" s="1"/>
       <c r="C223" s="1"/>
@@ -20465,8 +20675,9 @@
       <c r="L223" s="1"/>
       <c r="M223" s="1"/>
       <c r="N223" s="1"/>
-    </row>
-    <row r="224" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O223" s="1"/>
+    </row>
+    <row r="224" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A224" s="1"/>
       <c r="B224" s="1"/>
       <c r="C224" s="1"/>
@@ -20481,8 +20692,9 @@
       <c r="L224" s="1"/>
       <c r="M224" s="1"/>
       <c r="N224" s="1"/>
-    </row>
-    <row r="225" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O224" s="1"/>
+    </row>
+    <row r="225" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A225" s="1"/>
       <c r="B225" s="1"/>
       <c r="C225" s="1"/>
@@ -20497,8 +20709,9 @@
       <c r="L225" s="1"/>
       <c r="M225" s="1"/>
       <c r="N225" s="1"/>
-    </row>
-    <row r="226" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O225" s="1"/>
+    </row>
+    <row r="226" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A226" s="1"/>
       <c r="B226" s="1"/>
       <c r="C226" s="1"/>
@@ -20513,8 +20726,9 @@
       <c r="L226" s="1"/>
       <c r="M226" s="1"/>
       <c r="N226" s="1"/>
-    </row>
-    <row r="227" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O226" s="1"/>
+    </row>
+    <row r="227" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A227" s="1"/>
       <c r="B227" s="1"/>
       <c r="C227" s="1"/>
@@ -20529,8 +20743,9 @@
       <c r="L227" s="1"/>
       <c r="M227" s="1"/>
       <c r="N227" s="1"/>
-    </row>
-    <row r="228" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O227" s="1"/>
+    </row>
+    <row r="228" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A228" s="1"/>
       <c r="B228" s="1"/>
       <c r="C228" s="1"/>
@@ -20545,8 +20760,9 @@
       <c r="L228" s="1"/>
       <c r="M228" s="1"/>
       <c r="N228" s="1"/>
-    </row>
-    <row r="229" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O228" s="1"/>
+    </row>
+    <row r="229" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A229" s="1"/>
       <c r="B229" s="1"/>
       <c r="C229" s="1"/>
@@ -20561,8 +20777,9 @@
       <c r="L229" s="1"/>
       <c r="M229" s="1"/>
       <c r="N229" s="1"/>
-    </row>
-    <row r="230" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O229" s="1"/>
+    </row>
+    <row r="230" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A230" s="1"/>
       <c r="B230" s="1"/>
       <c r="C230" s="1"/>
@@ -20577,8 +20794,9 @@
       <c r="L230" s="1"/>
       <c r="M230" s="1"/>
       <c r="N230" s="1"/>
-    </row>
-    <row r="231" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O230" s="1"/>
+    </row>
+    <row r="231" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A231" s="1"/>
       <c r="B231" s="1"/>
       <c r="C231" s="1"/>
@@ -20593,8 +20811,9 @@
       <c r="L231" s="1"/>
       <c r="M231" s="1"/>
       <c r="N231" s="1"/>
-    </row>
-    <row r="232" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O231" s="1"/>
+    </row>
+    <row r="232" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A232" s="1"/>
       <c r="B232" s="1"/>
       <c r="C232" s="1"/>
@@ -20609,8 +20828,9 @@
       <c r="L232" s="1"/>
       <c r="M232" s="1"/>
       <c r="N232" s="1"/>
-    </row>
-    <row r="233" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O232" s="1"/>
+    </row>
+    <row r="233" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A233" s="1"/>
       <c r="B233" s="1"/>
       <c r="C233" s="1"/>
@@ -20625,8 +20845,9 @@
       <c r="L233" s="1"/>
       <c r="M233" s="1"/>
       <c r="N233" s="1"/>
-    </row>
-    <row r="234" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O233" s="1"/>
+    </row>
+    <row r="234" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A234" s="1"/>
       <c r="B234" s="1"/>
       <c r="C234" s="1"/>
@@ -20641,8 +20862,9 @@
       <c r="L234" s="1"/>
       <c r="M234" s="1"/>
       <c r="N234" s="1"/>
-    </row>
-    <row r="235" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O234" s="1"/>
+    </row>
+    <row r="235" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A235" s="1"/>
       <c r="B235" s="1"/>
       <c r="C235" s="1"/>
@@ -20657,8 +20879,9 @@
       <c r="L235" s="1"/>
       <c r="M235" s="1"/>
       <c r="N235" s="1"/>
-    </row>
-    <row r="236" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O235" s="1"/>
+    </row>
+    <row r="236" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A236" s="1"/>
       <c r="B236" s="1"/>
       <c r="C236" s="1"/>
@@ -20673,8 +20896,9 @@
       <c r="L236" s="1"/>
       <c r="M236" s="1"/>
       <c r="N236" s="1"/>
-    </row>
-    <row r="237" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O236" s="1"/>
+    </row>
+    <row r="237" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A237" s="1"/>
       <c r="B237" s="1"/>
       <c r="C237" s="1"/>
@@ -20689,8 +20913,9 @@
       <c r="L237" s="1"/>
       <c r="M237" s="1"/>
       <c r="N237" s="1"/>
-    </row>
-    <row r="238" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O237" s="1"/>
+    </row>
+    <row r="238" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A238" s="1"/>
       <c r="B238" s="1"/>
       <c r="C238" s="1"/>
@@ -20705,8 +20930,9 @@
       <c r="L238" s="1"/>
       <c r="M238" s="1"/>
       <c r="N238" s="1"/>
-    </row>
-    <row r="239" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O238" s="1"/>
+    </row>
+    <row r="239" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A239" s="1"/>
       <c r="B239" s="1"/>
       <c r="C239" s="1"/>
@@ -20721,8 +20947,9 @@
       <c r="L239" s="1"/>
       <c r="M239" s="1"/>
       <c r="N239" s="1"/>
-    </row>
-    <row r="240" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O239" s="1"/>
+    </row>
+    <row r="240" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A240" s="1"/>
       <c r="B240" s="1"/>
       <c r="C240" s="1"/>
@@ -20737,8 +20964,9 @@
       <c r="L240" s="1"/>
       <c r="M240" s="1"/>
       <c r="N240" s="1"/>
-    </row>
-    <row r="241" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O240" s="1"/>
+    </row>
+    <row r="241" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A241" s="1"/>
       <c r="B241" s="1"/>
       <c r="C241" s="1"/>
@@ -20753,8 +20981,9 @@
       <c r="L241" s="1"/>
       <c r="M241" s="1"/>
       <c r="N241" s="1"/>
-    </row>
-    <row r="242" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O241" s="1"/>
+    </row>
+    <row r="242" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A242" s="1"/>
       <c r="B242" s="1"/>
       <c r="C242" s="1"/>
@@ -20769,8 +20998,9 @@
       <c r="L242" s="1"/>
       <c r="M242" s="1"/>
       <c r="N242" s="1"/>
-    </row>
-    <row r="243" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O242" s="1"/>
+    </row>
+    <row r="243" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A243" s="1"/>
       <c r="B243" s="1"/>
       <c r="C243" s="1"/>
@@ -20785,8 +21015,9 @@
       <c r="L243" s="1"/>
       <c r="M243" s="1"/>
       <c r="N243" s="1"/>
-    </row>
-    <row r="244" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O243" s="1"/>
+    </row>
+    <row r="244" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A244" s="1"/>
       <c r="B244" s="1"/>
       <c r="C244" s="1"/>
@@ -20801,8 +21032,9 @@
       <c r="L244" s="1"/>
       <c r="M244" s="1"/>
       <c r="N244" s="1"/>
-    </row>
-    <row r="245" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O244" s="1"/>
+    </row>
+    <row r="245" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A245" s="1"/>
       <c r="B245" s="1"/>
       <c r="C245" s="1"/>
@@ -20817,8 +21049,9 @@
       <c r="L245" s="1"/>
       <c r="M245" s="1"/>
       <c r="N245" s="1"/>
-    </row>
-    <row r="246" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O245" s="1"/>
+    </row>
+    <row r="246" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A246" s="1"/>
       <c r="B246" s="1"/>
       <c r="C246" s="1"/>
@@ -20833,8 +21066,9 @@
       <c r="L246" s="1"/>
       <c r="M246" s="1"/>
       <c r="N246" s="1"/>
-    </row>
-    <row r="247" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O246" s="1"/>
+    </row>
+    <row r="247" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A247" s="1"/>
       <c r="B247" s="1"/>
       <c r="C247" s="1"/>
@@ -20849,8 +21083,9 @@
       <c r="L247" s="1"/>
       <c r="M247" s="1"/>
       <c r="N247" s="1"/>
-    </row>
-    <row r="248" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O247" s="1"/>
+    </row>
+    <row r="248" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A248" s="1"/>
       <c r="B248" s="1"/>
       <c r="C248" s="1"/>
@@ -20865,8 +21100,9 @@
       <c r="L248" s="1"/>
       <c r="M248" s="1"/>
       <c r="N248" s="1"/>
-    </row>
-    <row r="249" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O248" s="1"/>
+    </row>
+    <row r="249" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A249" s="1"/>
       <c r="B249" s="1"/>
       <c r="C249" s="1"/>
@@ -20881,8 +21117,9 @@
       <c r="L249" s="1"/>
       <c r="M249" s="1"/>
       <c r="N249" s="1"/>
-    </row>
-    <row r="250" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O249" s="1"/>
+    </row>
+    <row r="250" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A250" s="1"/>
       <c r="B250" s="1"/>
       <c r="C250" s="1"/>
@@ -20897,8 +21134,9 @@
       <c r="L250" s="1"/>
       <c r="M250" s="1"/>
       <c r="N250" s="1"/>
-    </row>
-    <row r="251" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O250" s="1"/>
+    </row>
+    <row r="251" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A251" s="1"/>
       <c r="B251" s="1"/>
       <c r="C251" s="1"/>
@@ -20913,8 +21151,9 @@
       <c r="L251" s="1"/>
       <c r="M251" s="1"/>
       <c r="N251" s="1"/>
-    </row>
-    <row r="252" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O251" s="1"/>
+    </row>
+    <row r="252" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A252" s="1"/>
       <c r="B252" s="1"/>
       <c r="C252" s="1"/>
@@ -20929,8 +21168,9 @@
       <c r="L252" s="1"/>
       <c r="M252" s="1"/>
       <c r="N252" s="1"/>
-    </row>
-    <row r="253" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O252" s="1"/>
+    </row>
+    <row r="253" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A253" s="1"/>
       <c r="B253" s="1"/>
       <c r="C253" s="1"/>
@@ -20945,8 +21185,9 @@
       <c r="L253" s="1"/>
       <c r="M253" s="1"/>
       <c r="N253" s="1"/>
-    </row>
-    <row r="254" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O253" s="1"/>
+    </row>
+    <row r="254" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A254" s="1"/>
       <c r="B254" s="1"/>
       <c r="C254" s="1"/>
@@ -20961,8 +21202,9 @@
       <c r="L254" s="1"/>
       <c r="M254" s="1"/>
       <c r="N254" s="1"/>
-    </row>
-    <row r="255" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O254" s="1"/>
+    </row>
+    <row r="255" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A255" s="1"/>
       <c r="B255" s="1"/>
       <c r="C255" s="1"/>
@@ -20977,8 +21219,9 @@
       <c r="L255" s="1"/>
       <c r="M255" s="1"/>
       <c r="N255" s="1"/>
-    </row>
-    <row r="256" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O255" s="1"/>
+    </row>
+    <row r="256" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A256" s="1"/>
       <c r="B256" s="1"/>
       <c r="C256" s="1"/>
@@ -20993,8 +21236,9 @@
       <c r="L256" s="1"/>
       <c r="M256" s="1"/>
       <c r="N256" s="1"/>
-    </row>
-    <row r="257" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O256" s="1"/>
+    </row>
+    <row r="257" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A257" s="1"/>
       <c r="B257" s="1"/>
       <c r="C257" s="1"/>
@@ -21009,8 +21253,9 @@
       <c r="L257" s="1"/>
       <c r="M257" s="1"/>
       <c r="N257" s="1"/>
-    </row>
-    <row r="258" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O257" s="1"/>
+    </row>
+    <row r="258" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A258" s="1"/>
       <c r="B258" s="1"/>
       <c r="C258" s="1"/>
@@ -21025,8 +21270,9 @@
       <c r="L258" s="1"/>
       <c r="M258" s="1"/>
       <c r="N258" s="1"/>
-    </row>
-    <row r="259" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O258" s="1"/>
+    </row>
+    <row r="259" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A259" s="1"/>
       <c r="B259" s="1"/>
       <c r="C259" s="1"/>
@@ -21041,8 +21287,9 @@
       <c r="L259" s="1"/>
       <c r="M259" s="1"/>
       <c r="N259" s="1"/>
-    </row>
-    <row r="260" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O259" s="1"/>
+    </row>
+    <row r="260" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A260" s="1"/>
       <c r="B260" s="1"/>
       <c r="C260" s="1"/>
@@ -21057,8 +21304,9 @@
       <c r="L260" s="1"/>
       <c r="M260" s="1"/>
       <c r="N260" s="1"/>
-    </row>
-    <row r="261" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O260" s="1"/>
+    </row>
+    <row r="261" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A261" s="1"/>
       <c r="B261" s="1"/>
       <c r="C261" s="1"/>
@@ -21073,8 +21321,9 @@
       <c r="L261" s="1"/>
       <c r="M261" s="1"/>
       <c r="N261" s="1"/>
-    </row>
-    <row r="262" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O261" s="1"/>
+    </row>
+    <row r="262" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A262" s="1"/>
       <c r="B262" s="1"/>
       <c r="C262" s="1"/>
@@ -21089,8 +21338,9 @@
       <c r="L262" s="1"/>
       <c r="M262" s="1"/>
       <c r="N262" s="1"/>
-    </row>
-    <row r="263" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O262" s="1"/>
+    </row>
+    <row r="263" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A263" s="1"/>
       <c r="B263" s="1"/>
       <c r="C263" s="1"/>
@@ -21105,8 +21355,9 @@
       <c r="L263" s="1"/>
       <c r="M263" s="1"/>
       <c r="N263" s="1"/>
-    </row>
-    <row r="264" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O263" s="1"/>
+    </row>
+    <row r="264" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A264" s="1"/>
       <c r="B264" s="1"/>
       <c r="C264" s="1"/>
@@ -21121,8 +21372,9 @@
       <c r="L264" s="1"/>
       <c r="M264" s="1"/>
       <c r="N264" s="1"/>
-    </row>
-    <row r="265" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O264" s="1"/>
+    </row>
+    <row r="265" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A265" s="1"/>
       <c r="B265" s="1"/>
       <c r="C265" s="1"/>
@@ -21137,8 +21389,9 @@
       <c r="L265" s="1"/>
       <c r="M265" s="1"/>
       <c r="N265" s="1"/>
-    </row>
-    <row r="266" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O265" s="1"/>
+    </row>
+    <row r="266" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A266" s="1"/>
       <c r="B266" s="1"/>
       <c r="C266" s="1"/>
@@ -21153,8 +21406,9 @@
       <c r="L266" s="1"/>
       <c r="M266" s="1"/>
       <c r="N266" s="1"/>
-    </row>
-    <row r="267" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O266" s="1"/>
+    </row>
+    <row r="267" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A267" s="1"/>
       <c r="B267" s="1"/>
       <c r="C267" s="1"/>
@@ -21169,8 +21423,9 @@
       <c r="L267" s="1"/>
       <c r="M267" s="1"/>
       <c r="N267" s="1"/>
-    </row>
-    <row r="268" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O267" s="1"/>
+    </row>
+    <row r="268" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A268" s="1"/>
       <c r="B268" s="1"/>
       <c r="C268" s="1"/>
@@ -21185,8 +21440,9 @@
       <c r="L268" s="1"/>
       <c r="M268" s="1"/>
       <c r="N268" s="1"/>
-    </row>
-    <row r="269" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O268" s="1"/>
+    </row>
+    <row r="269" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A269" s="1"/>
       <c r="B269" s="1"/>
       <c r="C269" s="1"/>
@@ -21201,8 +21457,9 @@
       <c r="L269" s="1"/>
       <c r="M269" s="1"/>
       <c r="N269" s="1"/>
-    </row>
-    <row r="270" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O269" s="1"/>
+    </row>
+    <row r="270" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A270" s="1"/>
       <c r="B270" s="1"/>
       <c r="C270" s="1"/>
@@ -21217,8 +21474,9 @@
       <c r="L270" s="1"/>
       <c r="M270" s="1"/>
       <c r="N270" s="1"/>
-    </row>
-    <row r="271" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O270" s="1"/>
+    </row>
+    <row r="271" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A271" s="1"/>
       <c r="B271" s="1"/>
       <c r="C271" s="1"/>
@@ -21233,8 +21491,9 @@
       <c r="L271" s="1"/>
       <c r="M271" s="1"/>
       <c r="N271" s="1"/>
-    </row>
-    <row r="272" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O271" s="1"/>
+    </row>
+    <row r="272" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A272" s="1"/>
       <c r="B272" s="1"/>
       <c r="C272" s="1"/>
@@ -21249,8 +21508,9 @@
       <c r="L272" s="1"/>
       <c r="M272" s="1"/>
       <c r="N272" s="1"/>
-    </row>
-    <row r="273" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O272" s="1"/>
+    </row>
+    <row r="273" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A273" s="1"/>
       <c r="B273" s="1"/>
       <c r="C273" s="1"/>
@@ -21265,8 +21525,9 @@
       <c r="L273" s="1"/>
       <c r="M273" s="1"/>
       <c r="N273" s="1"/>
-    </row>
-    <row r="274" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O273" s="1"/>
+    </row>
+    <row r="274" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A274" s="1"/>
       <c r="B274" s="1"/>
       <c r="C274" s="1"/>
@@ -21281,8 +21542,9 @@
       <c r="L274" s="1"/>
       <c r="M274" s="1"/>
       <c r="N274" s="1"/>
-    </row>
-    <row r="275" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O274" s="1"/>
+    </row>
+    <row r="275" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A275" s="1"/>
       <c r="B275" s="1"/>
       <c r="C275" s="1"/>
@@ -21297,8 +21559,9 @@
       <c r="L275" s="1"/>
       <c r="M275" s="1"/>
       <c r="N275" s="1"/>
-    </row>
-    <row r="276" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O275" s="1"/>
+    </row>
+    <row r="276" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A276" s="1"/>
       <c r="B276" s="1"/>
       <c r="C276" s="1"/>
@@ -21313,8 +21576,9 @@
       <c r="L276" s="1"/>
       <c r="M276" s="1"/>
       <c r="N276" s="1"/>
-    </row>
-    <row r="277" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O276" s="1"/>
+    </row>
+    <row r="277" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A277" s="1"/>
       <c r="B277" s="1"/>
       <c r="C277" s="1"/>
@@ -21329,8 +21593,9 @@
       <c r="L277" s="1"/>
       <c r="M277" s="1"/>
       <c r="N277" s="1"/>
-    </row>
-    <row r="278" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O277" s="1"/>
+    </row>
+    <row r="278" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A278" s="1"/>
       <c r="B278" s="1"/>
       <c r="C278" s="1"/>
@@ -21345,8 +21610,9 @@
       <c r="L278" s="1"/>
       <c r="M278" s="1"/>
       <c r="N278" s="1"/>
-    </row>
-    <row r="279" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O278" s="1"/>
+    </row>
+    <row r="279" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A279" s="1"/>
       <c r="B279" s="1"/>
       <c r="C279" s="1"/>
@@ -21361,8 +21627,9 @@
       <c r="L279" s="1"/>
       <c r="M279" s="1"/>
       <c r="N279" s="1"/>
-    </row>
-    <row r="280" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O279" s="1"/>
+    </row>
+    <row r="280" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A280" s="1"/>
       <c r="B280" s="1"/>
       <c r="C280" s="1"/>
@@ -21377,8 +21644,9 @@
       <c r="L280" s="1"/>
       <c r="M280" s="1"/>
       <c r="N280" s="1"/>
-    </row>
-    <row r="281" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O280" s="1"/>
+    </row>
+    <row r="281" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A281" s="1"/>
       <c r="B281" s="1"/>
       <c r="C281" s="1"/>
@@ -21393,8 +21661,9 @@
       <c r="L281" s="1"/>
       <c r="M281" s="1"/>
       <c r="N281" s="1"/>
-    </row>
-    <row r="282" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O281" s="1"/>
+    </row>
+    <row r="282" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A282" s="1"/>
       <c r="B282" s="1"/>
       <c r="C282" s="1"/>
@@ -21409,8 +21678,9 @@
       <c r="L282" s="1"/>
       <c r="M282" s="1"/>
       <c r="N282" s="1"/>
-    </row>
-    <row r="283" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O282" s="1"/>
+    </row>
+    <row r="283" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A283" s="1"/>
       <c r="B283" s="1"/>
       <c r="C283" s="1"/>
@@ -21425,8 +21695,9 @@
       <c r="L283" s="1"/>
       <c r="M283" s="1"/>
       <c r="N283" s="1"/>
-    </row>
-    <row r="284" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O283" s="1"/>
+    </row>
+    <row r="284" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A284" s="1"/>
       <c r="B284" s="1"/>
       <c r="C284" s="1"/>
@@ -21441,8 +21712,9 @@
       <c r="L284" s="1"/>
       <c r="M284" s="1"/>
       <c r="N284" s="1"/>
-    </row>
-    <row r="285" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O284" s="1"/>
+    </row>
+    <row r="285" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A285" s="1"/>
       <c r="B285" s="1"/>
       <c r="C285" s="1"/>
@@ -21457,8 +21729,9 @@
       <c r="L285" s="1"/>
       <c r="M285" s="1"/>
       <c r="N285" s="1"/>
-    </row>
-    <row r="286" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O285" s="1"/>
+    </row>
+    <row r="286" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A286" s="1"/>
       <c r="B286" s="1"/>
       <c r="C286" s="1"/>
@@ -21473,8 +21746,9 @@
       <c r="L286" s="1"/>
       <c r="M286" s="1"/>
       <c r="N286" s="1"/>
-    </row>
-    <row r="287" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O286" s="1"/>
+    </row>
+    <row r="287" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A287" s="1"/>
       <c r="B287" s="1"/>
       <c r="C287" s="1"/>
@@ -21489,8 +21763,9 @@
       <c r="L287" s="1"/>
       <c r="M287" s="1"/>
       <c r="N287" s="1"/>
-    </row>
-    <row r="288" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O287" s="1"/>
+    </row>
+    <row r="288" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A288" s="1"/>
       <c r="B288" s="1"/>
       <c r="C288" s="1"/>
@@ -21505,8 +21780,9 @@
       <c r="L288" s="1"/>
       <c r="M288" s="1"/>
       <c r="N288" s="1"/>
-    </row>
-    <row r="289" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O288" s="1"/>
+    </row>
+    <row r="289" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A289" s="1"/>
       <c r="B289" s="1"/>
       <c r="C289" s="1"/>
@@ -21521,8 +21797,9 @@
       <c r="L289" s="1"/>
       <c r="M289" s="1"/>
       <c r="N289" s="1"/>
-    </row>
-    <row r="290" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O289" s="1"/>
+    </row>
+    <row r="290" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A290" s="1"/>
       <c r="B290" s="1"/>
       <c r="C290" s="1"/>
@@ -21537,8 +21814,9 @@
       <c r="L290" s="1"/>
       <c r="M290" s="1"/>
       <c r="N290" s="1"/>
-    </row>
-    <row r="291" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O290" s="1"/>
+    </row>
+    <row r="291" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A291" s="1"/>
       <c r="B291" s="1"/>
       <c r="C291" s="1"/>
@@ -21553,8 +21831,9 @@
       <c r="L291" s="1"/>
       <c r="M291" s="1"/>
       <c r="N291" s="1"/>
-    </row>
-    <row r="292" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O291" s="1"/>
+    </row>
+    <row r="292" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A292" s="1"/>
       <c r="B292" s="1"/>
       <c r="C292" s="1"/>
@@ -21569,8 +21848,9 @@
       <c r="L292" s="1"/>
       <c r="M292" s="1"/>
       <c r="N292" s="1"/>
-    </row>
-    <row r="293" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O292" s="1"/>
+    </row>
+    <row r="293" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A293" s="1"/>
       <c r="B293" s="1"/>
       <c r="C293" s="1"/>
@@ -21585,8 +21865,9 @@
       <c r="L293" s="1"/>
       <c r="M293" s="1"/>
       <c r="N293" s="1"/>
-    </row>
-    <row r="294" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O293" s="1"/>
+    </row>
+    <row r="294" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A294" s="1"/>
       <c r="B294" s="1"/>
       <c r="C294" s="1"/>
@@ -21601,8 +21882,9 @@
       <c r="L294" s="1"/>
       <c r="M294" s="1"/>
       <c r="N294" s="1"/>
-    </row>
-    <row r="295" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O294" s="1"/>
+    </row>
+    <row r="295" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A295" s="1"/>
       <c r="B295" s="1"/>
       <c r="C295" s="1"/>
@@ -21617,8 +21899,9 @@
       <c r="L295" s="1"/>
       <c r="M295" s="1"/>
       <c r="N295" s="1"/>
-    </row>
-    <row r="296" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O295" s="1"/>
+    </row>
+    <row r="296" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A296" s="1"/>
       <c r="B296" s="1"/>
       <c r="C296" s="1"/>
@@ -21633,8 +21916,9 @@
       <c r="L296" s="1"/>
       <c r="M296" s="1"/>
       <c r="N296" s="1"/>
-    </row>
-    <row r="297" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O296" s="1"/>
+    </row>
+    <row r="297" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A297" s="1"/>
       <c r="B297" s="1"/>
       <c r="C297" s="1"/>
@@ -21649,8 +21933,9 @@
       <c r="L297" s="1"/>
       <c r="M297" s="1"/>
       <c r="N297" s="1"/>
-    </row>
-    <row r="298" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O297" s="1"/>
+    </row>
+    <row r="298" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A298" s="1"/>
       <c r="B298" s="1"/>
       <c r="C298" s="1"/>
@@ -21665,8 +21950,9 @@
       <c r="L298" s="1"/>
       <c r="M298" s="1"/>
       <c r="N298" s="1"/>
-    </row>
-    <row r="299" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O298" s="1"/>
+    </row>
+    <row r="299" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A299" s="1"/>
       <c r="B299" s="1"/>
       <c r="C299" s="1"/>
@@ -21681,8 +21967,9 @@
       <c r="L299" s="1"/>
       <c r="M299" s="1"/>
       <c r="N299" s="1"/>
-    </row>
-    <row r="300" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O299" s="1"/>
+    </row>
+    <row r="300" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A300" s="1"/>
       <c r="B300" s="1"/>
       <c r="C300" s="1"/>
@@ -21697,8 +21984,9 @@
       <c r="L300" s="1"/>
       <c r="M300" s="1"/>
       <c r="N300" s="1"/>
-    </row>
-    <row r="301" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O300" s="1"/>
+    </row>
+    <row r="301" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A301" s="1"/>
       <c r="B301" s="1"/>
       <c r="C301" s="1"/>
@@ -21713,8 +22001,9 @@
       <c r="L301" s="1"/>
       <c r="M301" s="1"/>
       <c r="N301" s="1"/>
-    </row>
-    <row r="302" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O301" s="1"/>
+    </row>
+    <row r="302" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A302" s="1"/>
       <c r="B302" s="1"/>
       <c r="C302" s="1"/>
@@ -21729,8 +22018,9 @@
       <c r="L302" s="1"/>
       <c r="M302" s="1"/>
       <c r="N302" s="1"/>
-    </row>
-    <row r="303" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O302" s="1"/>
+    </row>
+    <row r="303" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A303" s="1"/>
       <c r="B303" s="1"/>
       <c r="C303" s="1"/>
@@ -21745,8 +22035,9 @@
       <c r="L303" s="1"/>
       <c r="M303" s="1"/>
       <c r="N303" s="1"/>
-    </row>
-    <row r="304" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O303" s="1"/>
+    </row>
+    <row r="304" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A304" s="1"/>
       <c r="B304" s="1"/>
       <c r="C304" s="1"/>
@@ -21761,8 +22052,9 @@
       <c r="L304" s="1"/>
       <c r="M304" s="1"/>
       <c r="N304" s="1"/>
-    </row>
-    <row r="305" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O304" s="1"/>
+    </row>
+    <row r="305" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A305" s="1"/>
       <c r="B305" s="1"/>
       <c r="C305" s="1"/>
@@ -21777,8 +22069,9 @@
       <c r="L305" s="1"/>
       <c r="M305" s="1"/>
       <c r="N305" s="1"/>
-    </row>
-    <row r="306" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O305" s="1"/>
+    </row>
+    <row r="306" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A306" s="1"/>
       <c r="B306" s="1"/>
       <c r="C306" s="1"/>
@@ -21793,8 +22086,9 @@
       <c r="L306" s="1"/>
       <c r="M306" s="1"/>
       <c r="N306" s="1"/>
-    </row>
-    <row r="307" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O306" s="1"/>
+    </row>
+    <row r="307" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A307" s="1"/>
       <c r="B307" s="1"/>
       <c r="C307" s="1"/>
@@ -21809,8 +22103,9 @@
       <c r="L307" s="1"/>
       <c r="M307" s="1"/>
       <c r="N307" s="1"/>
-    </row>
-    <row r="308" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O307" s="1"/>
+    </row>
+    <row r="308" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A308" s="1"/>
       <c r="B308" s="1"/>
       <c r="C308" s="1"/>
@@ -21825,8 +22120,9 @@
       <c r="L308" s="1"/>
       <c r="M308" s="1"/>
       <c r="N308" s="1"/>
-    </row>
-    <row r="309" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O308" s="1"/>
+    </row>
+    <row r="309" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A309" s="1"/>
       <c r="B309" s="1"/>
       <c r="C309" s="1"/>
@@ -21841,8 +22137,9 @@
       <c r="L309" s="1"/>
       <c r="M309" s="1"/>
       <c r="N309" s="1"/>
-    </row>
-    <row r="310" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O309" s="1"/>
+    </row>
+    <row r="310" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A310" s="1"/>
       <c r="B310" s="1"/>
       <c r="C310" s="1"/>
@@ -21857,8 +22154,9 @@
       <c r="L310" s="1"/>
       <c r="M310" s="1"/>
       <c r="N310" s="1"/>
-    </row>
-    <row r="311" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O310" s="1"/>
+    </row>
+    <row r="311" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A311" s="1"/>
       <c r="B311" s="1"/>
       <c r="C311" s="1"/>
@@ -21873,8 +22171,9 @@
       <c r="L311" s="1"/>
       <c r="M311" s="1"/>
       <c r="N311" s="1"/>
-    </row>
-    <row r="312" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O311" s="1"/>
+    </row>
+    <row r="312" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A312" s="1"/>
       <c r="B312" s="1"/>
       <c r="C312" s="1"/>
@@ -21889,8 +22188,9 @@
       <c r="L312" s="1"/>
       <c r="M312" s="1"/>
       <c r="N312" s="1"/>
-    </row>
-    <row r="313" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O312" s="1"/>
+    </row>
+    <row r="313" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A313" s="1"/>
       <c r="B313" s="1"/>
       <c r="C313" s="1"/>
@@ -21905,8 +22205,9 @@
       <c r="L313" s="1"/>
       <c r="M313" s="1"/>
       <c r="N313" s="1"/>
-    </row>
-    <row r="314" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O313" s="1"/>
+    </row>
+    <row r="314" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A314" s="1"/>
       <c r="B314" s="1"/>
       <c r="C314" s="1"/>
@@ -21921,8 +22222,9 @@
       <c r="L314" s="1"/>
       <c r="M314" s="1"/>
       <c r="N314" s="1"/>
-    </row>
-    <row r="315" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O314" s="1"/>
+    </row>
+    <row r="315" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A315" s="1"/>
       <c r="B315" s="1"/>
       <c r="C315" s="1"/>
@@ -21937,8 +22239,9 @@
       <c r="L315" s="1"/>
       <c r="M315" s="1"/>
       <c r="N315" s="1"/>
-    </row>
-    <row r="316" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O315" s="1"/>
+    </row>
+    <row r="316" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A316" s="1"/>
       <c r="B316" s="1"/>
       <c r="C316" s="1"/>
@@ -21953,8 +22256,9 @@
       <c r="L316" s="1"/>
       <c r="M316" s="1"/>
       <c r="N316" s="1"/>
-    </row>
-    <row r="317" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O316" s="1"/>
+    </row>
+    <row r="317" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A317" s="1"/>
       <c r="B317" s="1"/>
       <c r="C317" s="1"/>
@@ -21969,8 +22273,9 @@
       <c r="L317" s="1"/>
       <c r="M317" s="1"/>
       <c r="N317" s="1"/>
-    </row>
-    <row r="318" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O317" s="1"/>
+    </row>
+    <row r="318" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A318" s="1"/>
       <c r="B318" s="1"/>
       <c r="C318" s="1"/>
@@ -21985,8 +22290,9 @@
       <c r="L318" s="1"/>
       <c r="M318" s="1"/>
       <c r="N318" s="1"/>
-    </row>
-    <row r="319" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O318" s="1"/>
+    </row>
+    <row r="319" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A319" s="1"/>
       <c r="B319" s="1"/>
       <c r="C319" s="1"/>
@@ -22001,8 +22307,9 @@
       <c r="L319" s="1"/>
       <c r="M319" s="1"/>
       <c r="N319" s="1"/>
-    </row>
-    <row r="320" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O319" s="1"/>
+    </row>
+    <row r="320" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A320" s="1"/>
       <c r="B320" s="1"/>
       <c r="C320" s="1"/>
@@ -22017,8 +22324,9 @@
       <c r="L320" s="1"/>
       <c r="M320" s="1"/>
       <c r="N320" s="1"/>
-    </row>
-    <row r="321" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O320" s="1"/>
+    </row>
+    <row r="321" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A321" s="1"/>
       <c r="B321" s="1"/>
       <c r="C321" s="1"/>
@@ -22033,8 +22341,9 @@
       <c r="L321" s="1"/>
       <c r="M321" s="1"/>
       <c r="N321" s="1"/>
-    </row>
-    <row r="322" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O321" s="1"/>
+    </row>
+    <row r="322" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A322" s="1"/>
       <c r="B322" s="1"/>
       <c r="C322" s="1"/>
@@ -22049,8 +22358,9 @@
       <c r="L322" s="1"/>
       <c r="M322" s="1"/>
       <c r="N322" s="1"/>
-    </row>
-    <row r="323" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O322" s="1"/>
+    </row>
+    <row r="323" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A323" s="1"/>
       <c r="B323" s="1"/>
       <c r="C323" s="1"/>
@@ -22065,8 +22375,9 @@
       <c r="L323" s="1"/>
       <c r="M323" s="1"/>
       <c r="N323" s="1"/>
-    </row>
-    <row r="324" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O323" s="1"/>
+    </row>
+    <row r="324" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A324" s="1"/>
       <c r="B324" s="1"/>
       <c r="C324" s="1"/>
@@ -22081,8 +22392,9 @@
       <c r="L324" s="1"/>
       <c r="M324" s="1"/>
       <c r="N324" s="1"/>
-    </row>
-    <row r="325" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O324" s="1"/>
+    </row>
+    <row r="325" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A325" s="1"/>
       <c r="B325" s="1"/>
       <c r="C325" s="1"/>
@@ -22097,8 +22409,9 @@
       <c r="L325" s="1"/>
       <c r="M325" s="1"/>
       <c r="N325" s="1"/>
-    </row>
-    <row r="326" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O325" s="1"/>
+    </row>
+    <row r="326" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A326" s="1"/>
       <c r="B326" s="1"/>
       <c r="C326" s="1"/>
@@ -22113,8 +22426,9 @@
       <c r="L326" s="1"/>
       <c r="M326" s="1"/>
       <c r="N326" s="1"/>
-    </row>
-    <row r="327" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O326" s="1"/>
+    </row>
+    <row r="327" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A327" s="1"/>
       <c r="B327" s="1"/>
       <c r="C327" s="1"/>
@@ -22129,8 +22443,9 @@
       <c r="L327" s="1"/>
       <c r="M327" s="1"/>
       <c r="N327" s="1"/>
-    </row>
-    <row r="328" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O327" s="1"/>
+    </row>
+    <row r="328" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A328" s="1"/>
       <c r="B328" s="1"/>
       <c r="C328" s="1"/>
@@ -22145,8 +22460,9 @@
       <c r="L328" s="1"/>
       <c r="M328" s="1"/>
       <c r="N328" s="1"/>
-    </row>
-    <row r="329" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O328" s="1"/>
+    </row>
+    <row r="329" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A329" s="1"/>
       <c r="B329" s="1"/>
       <c r="C329" s="1"/>
@@ -22161,8 +22477,9 @@
       <c r="L329" s="1"/>
       <c r="M329" s="1"/>
       <c r="N329" s="1"/>
-    </row>
-    <row r="330" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O329" s="1"/>
+    </row>
+    <row r="330" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A330" s="1"/>
       <c r="B330" s="1"/>
       <c r="C330" s="1"/>
@@ -22177,8 +22494,9 @@
       <c r="L330" s="1"/>
       <c r="M330" s="1"/>
       <c r="N330" s="1"/>
-    </row>
-    <row r="331" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O330" s="1"/>
+    </row>
+    <row r="331" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A331" s="1"/>
       <c r="B331" s="1"/>
       <c r="C331" s="1"/>
@@ -22193,8 +22511,9 @@
       <c r="L331" s="1"/>
       <c r="M331" s="1"/>
       <c r="N331" s="1"/>
-    </row>
-    <row r="332" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O331" s="1"/>
+    </row>
+    <row r="332" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A332" s="1"/>
       <c r="B332" s="1"/>
       <c r="C332" s="1"/>
@@ -22209,8 +22528,9 @@
       <c r="L332" s="1"/>
       <c r="M332" s="1"/>
       <c r="N332" s="1"/>
-    </row>
-    <row r="333" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O332" s="1"/>
+    </row>
+    <row r="333" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A333" s="1"/>
       <c r="B333" s="1"/>
       <c r="C333" s="1"/>
@@ -22225,8 +22545,9 @@
       <c r="L333" s="1"/>
       <c r="M333" s="1"/>
       <c r="N333" s="1"/>
-    </row>
-    <row r="334" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O333" s="1"/>
+    </row>
+    <row r="334" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A334" s="1"/>
       <c r="B334" s="1"/>
       <c r="C334" s="1"/>
@@ -22241,8 +22562,9 @@
       <c r="L334" s="1"/>
       <c r="M334" s="1"/>
       <c r="N334" s="1"/>
-    </row>
-    <row r="335" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O334" s="1"/>
+    </row>
+    <row r="335" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A335" s="1"/>
       <c r="B335" s="1"/>
       <c r="C335" s="1"/>
@@ -22257,8 +22579,9 @@
       <c r="L335" s="1"/>
       <c r="M335" s="1"/>
       <c r="N335" s="1"/>
-    </row>
-    <row r="336" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O335" s="1"/>
+    </row>
+    <row r="336" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A336" s="1"/>
       <c r="B336" s="1"/>
       <c r="C336" s="1"/>
@@ -22273,8 +22596,9 @@
       <c r="L336" s="1"/>
       <c r="M336" s="1"/>
       <c r="N336" s="1"/>
-    </row>
-    <row r="337" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O336" s="1"/>
+    </row>
+    <row r="337" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A337" s="1"/>
       <c r="B337" s="1"/>
       <c r="C337" s="1"/>
@@ -22289,8 +22613,9 @@
       <c r="L337" s="1"/>
       <c r="M337" s="1"/>
       <c r="N337" s="1"/>
-    </row>
-    <row r="338" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O337" s="1"/>
+    </row>
+    <row r="338" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A338" s="1"/>
       <c r="B338" s="1"/>
       <c r="C338" s="1"/>
@@ -22305,8 +22630,9 @@
       <c r="L338" s="1"/>
       <c r="M338" s="1"/>
       <c r="N338" s="1"/>
-    </row>
-    <row r="339" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O338" s="1"/>
+    </row>
+    <row r="339" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A339" s="1"/>
       <c r="B339" s="1"/>
       <c r="C339" s="1"/>
@@ -22321,8 +22647,9 @@
       <c r="L339" s="1"/>
       <c r="M339" s="1"/>
       <c r="N339" s="1"/>
-    </row>
-    <row r="340" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O339" s="1"/>
+    </row>
+    <row r="340" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A340" s="1"/>
       <c r="B340" s="1"/>
       <c r="C340" s="1"/>
@@ -22337,8 +22664,9 @@
       <c r="L340" s="1"/>
       <c r="M340" s="1"/>
       <c r="N340" s="1"/>
-    </row>
-    <row r="341" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O340" s="1"/>
+    </row>
+    <row r="341" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A341" s="1"/>
       <c r="B341" s="1"/>
       <c r="C341" s="1"/>
@@ -22353,8 +22681,9 @@
       <c r="L341" s="1"/>
       <c r="M341" s="1"/>
       <c r="N341" s="1"/>
-    </row>
-    <row r="342" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O341" s="1"/>
+    </row>
+    <row r="342" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A342" s="1"/>
       <c r="B342" s="1"/>
       <c r="C342" s="1"/>
@@ -22369,8 +22698,9 @@
       <c r="L342" s="1"/>
       <c r="M342" s="1"/>
       <c r="N342" s="1"/>
-    </row>
-    <row r="343" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O342" s="1"/>
+    </row>
+    <row r="343" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A343" s="1"/>
       <c r="B343" s="1"/>
       <c r="C343" s="1"/>
@@ -22385,8 +22715,9 @@
       <c r="L343" s="1"/>
       <c r="M343" s="1"/>
       <c r="N343" s="1"/>
-    </row>
-    <row r="344" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O343" s="1"/>
+    </row>
+    <row r="344" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A344" s="1"/>
       <c r="B344" s="1"/>
       <c r="C344" s="1"/>
@@ -22401,8 +22732,9 @@
       <c r="L344" s="1"/>
       <c r="M344" s="1"/>
       <c r="N344" s="1"/>
-    </row>
-    <row r="345" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O344" s="1"/>
+    </row>
+    <row r="345" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A345" s="1"/>
       <c r="B345" s="1"/>
       <c r="C345" s="1"/>
@@ -22417,8 +22749,9 @@
       <c r="L345" s="1"/>
       <c r="M345" s="1"/>
       <c r="N345" s="1"/>
-    </row>
-    <row r="346" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O345" s="1"/>
+    </row>
+    <row r="346" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A346" s="1"/>
       <c r="B346" s="1"/>
       <c r="C346" s="1"/>
@@ -22432,8 +22765,9 @@
       <c r="L346" s="1"/>
       <c r="M346" s="1"/>
       <c r="N346" s="1"/>
-    </row>
-    <row r="347" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O346" s="1"/>
+    </row>
+    <row r="347" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A347" s="1"/>
       <c r="B347" s="1"/>
       <c r="C347" s="1"/>
@@ -22447,8 +22781,9 @@
       <c r="L347" s="1"/>
       <c r="M347" s="1"/>
       <c r="N347" s="1"/>
-    </row>
-    <row r="348" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O347" s="1"/>
+    </row>
+    <row r="348" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A348" s="1"/>
       <c r="B348" s="1"/>
       <c r="C348" s="1"/>
@@ -22462,8 +22797,9 @@
       <c r="L348" s="1"/>
       <c r="M348" s="1"/>
       <c r="N348" s="1"/>
-    </row>
-    <row r="349" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O348" s="1"/>
+    </row>
+    <row r="349" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A349" s="1"/>
       <c r="B349" s="1"/>
       <c r="C349" s="1"/>
@@ -22476,8 +22812,9 @@
       <c r="K349" s="1"/>
       <c r="L349" s="1"/>
       <c r="M349" s="1"/>
-    </row>
-    <row r="350" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="N349" s="1"/>
+    </row>
+    <row r="350" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A350" s="1"/>
       <c r="B350" s="1"/>
       <c r="C350" s="1"/>
@@ -22490,8 +22827,9 @@
       <c r="K350" s="1"/>
       <c r="L350" s="1"/>
       <c r="M350" s="1"/>
-    </row>
-    <row r="351" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="N350" s="1"/>
+    </row>
+    <row r="351" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A351" s="1"/>
       <c r="B351" s="1"/>
       <c r="C351" s="1"/>
@@ -22504,8 +22842,9 @@
       <c r="K351" s="1"/>
       <c r="L351" s="1"/>
       <c r="M351" s="1"/>
-    </row>
-    <row r="352" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="N351" s="1"/>
+    </row>
+    <row r="352" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A352" s="1"/>
       <c r="B352" s="1"/>
       <c r="C352" s="1"/>
@@ -22515,9 +22854,10 @@
       <c r="H352" s="1"/>
       <c r="I352" s="1"/>
       <c r="J352" s="1"/>
-      <c r="M352" s="1"/>
-    </row>
-    <row r="353" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="K352" s="1"/>
+      <c r="N352" s="1"/>
+    </row>
+    <row r="353" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A353" s="1"/>
       <c r="B353" s="1"/>
       <c r="C353" s="1"/>
@@ -22527,9 +22867,10 @@
       <c r="H353" s="1"/>
       <c r="I353" s="1"/>
       <c r="J353" s="1"/>
-      <c r="M353" s="1"/>
-    </row>
-    <row r="354" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="K353" s="1"/>
+      <c r="N353" s="1"/>
+    </row>
+    <row r="354" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A354" s="1"/>
       <c r="B354" s="1"/>
       <c r="C354" s="1"/>
@@ -22539,9 +22880,10 @@
       <c r="H354" s="1"/>
       <c r="I354" s="1"/>
       <c r="J354" s="1"/>
-      <c r="M354" s="1"/>
-    </row>
-    <row r="355" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="K354" s="1"/>
+      <c r="N354" s="1"/>
+    </row>
+    <row r="355" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A355" s="1"/>
       <c r="B355" s="1"/>
       <c r="C355" s="1"/>
@@ -22549,7 +22891,7 @@
       <c r="H355" s="1"/>
       <c r="I355" s="1"/>
       <c r="J355" s="1"/>
-      <c r="M355" s="1"/>
+      <c r="N355" s="1"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
